--- a/backend/data/boreholes/地层汇总.xlsx
+++ b/backend/data/boreholes/地层汇总.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\GeoMine3D\backend\data\boreholes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431BF123-F3EA-4540-838E-01D023DF0D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8ADAAD-7A6E-4A55-8A70-4030CAA5D998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3516" yWindow="3240" windowWidth="23040" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4128" yWindow="3036" windowWidth="23040" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3524" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3476" uniqueCount="196">
   <si>
     <t>钻孔名称</t>
   </si>
@@ -441,9 +441,6 @@
     <t>J409</t>
   </si>
   <si>
-    <t>J410</t>
-  </si>
-  <si>
     <t>J413</t>
   </si>
   <si>
@@ -532,12 +529,6 @@
   </si>
   <si>
     <t>J706</t>
-  </si>
-  <si>
-    <t>J706-1</t>
-  </si>
-  <si>
-    <t>J706-2</t>
   </si>
   <si>
     <t>J707</t>
@@ -999,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1761"/>
+  <dimension ref="A1:D1737"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
@@ -17208,10 +17199,10 @@
         <v>5</v>
       </c>
       <c r="C1158">
-        <v>6.85</v>
+        <v>13.9</v>
       </c>
       <c r="D1158">
-        <v>6.85</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="1159" spans="1:4" x14ac:dyDescent="0.25">
@@ -17222,10 +17213,10 @@
         <v>6</v>
       </c>
       <c r="C1159">
-        <v>31.5</v>
+        <v>92.9</v>
       </c>
       <c r="D1159">
-        <v>24.65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1160" spans="1:4" x14ac:dyDescent="0.25">
@@ -17236,10 +17227,10 @@
         <v>7</v>
       </c>
       <c r="C1160">
-        <v>87.75</v>
+        <v>146.4</v>
       </c>
       <c r="D1160">
-        <v>56.25</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1161" spans="1:4" x14ac:dyDescent="0.25">
@@ -17250,10 +17241,10 @@
         <v>8</v>
       </c>
       <c r="C1161">
-        <v>102.7</v>
+        <v>156</v>
       </c>
       <c r="D1161">
-        <v>14.95</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="1162" spans="1:4" x14ac:dyDescent="0.25">
@@ -17264,10 +17255,10 @@
         <v>9</v>
       </c>
       <c r="C1162">
-        <v>117.54</v>
+        <v>170.73</v>
       </c>
       <c r="D1162">
-        <v>14.84</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="1163" spans="1:4" x14ac:dyDescent="0.25">
@@ -17278,10 +17269,10 @@
         <v>10</v>
       </c>
       <c r="C1163">
-        <v>118.04</v>
+        <v>170.73</v>
       </c>
       <c r="D1163">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1164" spans="1:4" x14ac:dyDescent="0.25">
@@ -17292,10 +17283,10 @@
         <v>11</v>
       </c>
       <c r="C1164">
-        <v>121.3</v>
+        <v>173.73</v>
       </c>
       <c r="D1164">
-        <v>3.26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1165" spans="1:4" x14ac:dyDescent="0.25">
@@ -17306,10 +17297,10 @@
         <v>12</v>
       </c>
       <c r="C1165">
-        <v>121.3</v>
+        <v>183.5</v>
       </c>
       <c r="D1165">
-        <v>0</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="1166" spans="1:4" x14ac:dyDescent="0.25">
@@ -17320,10 +17311,10 @@
         <v>13</v>
       </c>
       <c r="C1166">
-        <v>163.84</v>
+        <v>189.23</v>
       </c>
       <c r="D1166">
-        <v>42.54</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="1167" spans="1:4" x14ac:dyDescent="0.25">
@@ -17334,10 +17325,10 @@
         <v>14</v>
       </c>
       <c r="C1167">
-        <v>163.84</v>
+        <v>216.63</v>
       </c>
       <c r="D1167">
-        <v>0</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="1168" spans="1:4" x14ac:dyDescent="0.25">
@@ -17348,10 +17339,10 @@
         <v>5</v>
       </c>
       <c r="C1168">
-        <v>13.9</v>
+        <v>16.52</v>
       </c>
       <c r="D1168">
-        <v>13.9</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="1169" spans="1:4" x14ac:dyDescent="0.25">
@@ -17362,10 +17353,10 @@
         <v>6</v>
       </c>
       <c r="C1169">
-        <v>92.9</v>
+        <v>75.66</v>
       </c>
       <c r="D1169">
-        <v>79</v>
+        <v>59.14</v>
       </c>
     </row>
     <row r="1170" spans="1:4" x14ac:dyDescent="0.25">
@@ -17376,10 +17367,10 @@
         <v>7</v>
       </c>
       <c r="C1170">
-        <v>146.4</v>
+        <v>96.03</v>
       </c>
       <c r="D1170">
-        <v>53.5</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="1171" spans="1:4" x14ac:dyDescent="0.25">
@@ -17390,10 +17381,10 @@
         <v>8</v>
       </c>
       <c r="C1171">
-        <v>156</v>
+        <v>120.2</v>
       </c>
       <c r="D1171">
-        <v>9.6</v>
+        <v>24.17</v>
       </c>
     </row>
     <row r="1172" spans="1:4" x14ac:dyDescent="0.25">
@@ -17404,10 +17395,10 @@
         <v>9</v>
       </c>
       <c r="C1172">
-        <v>170.73</v>
+        <v>127</v>
       </c>
       <c r="D1172">
-        <v>14.73</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="1173" spans="1:4" x14ac:dyDescent="0.25">
@@ -17418,10 +17409,10 @@
         <v>10</v>
       </c>
       <c r="C1173">
-        <v>170.73</v>
+        <v>128.4</v>
       </c>
       <c r="D1173">
-        <v>0</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="1174" spans="1:4" x14ac:dyDescent="0.25">
@@ -17432,10 +17423,10 @@
         <v>11</v>
       </c>
       <c r="C1174">
-        <v>173.73</v>
+        <v>131.69999999999999</v>
       </c>
       <c r="D1174">
-        <v>3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="1175" spans="1:4" x14ac:dyDescent="0.25">
@@ -17446,10 +17437,10 @@
         <v>12</v>
       </c>
       <c r="C1175">
-        <v>183.5</v>
+        <v>131.69999999999999</v>
       </c>
       <c r="D1175">
-        <v>9.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1176" spans="1:4" x14ac:dyDescent="0.25">
@@ -17460,10 +17451,10 @@
         <v>13</v>
       </c>
       <c r="C1176">
-        <v>189.23</v>
+        <v>164.3</v>
       </c>
       <c r="D1176">
-        <v>5.73</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="1177" spans="1:4" x14ac:dyDescent="0.25">
@@ -17474,10 +17465,10 @@
         <v>14</v>
       </c>
       <c r="C1177">
-        <v>216.63</v>
+        <v>165.18</v>
       </c>
       <c r="D1177">
-        <v>27.4</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="1178" spans="1:4" x14ac:dyDescent="0.25">
@@ -17488,10 +17479,10 @@
         <v>5</v>
       </c>
       <c r="C1178">
-        <v>16.52</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D1178">
-        <v>16.52</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="1179" spans="1:4" x14ac:dyDescent="0.25">
@@ -17502,10 +17493,10 @@
         <v>6</v>
       </c>
       <c r="C1179">
-        <v>75.66</v>
+        <v>62.33</v>
       </c>
       <c r="D1179">
-        <v>59.14</v>
+        <v>60.13</v>
       </c>
     </row>
     <row r="1180" spans="1:4" x14ac:dyDescent="0.25">
@@ -17516,10 +17507,10 @@
         <v>7</v>
       </c>
       <c r="C1180">
-        <v>96.03</v>
+        <v>85.4</v>
       </c>
       <c r="D1180">
-        <v>20.37</v>
+        <v>23.07</v>
       </c>
     </row>
     <row r="1181" spans="1:4" x14ac:dyDescent="0.25">
@@ -17530,10 +17521,10 @@
         <v>8</v>
       </c>
       <c r="C1181">
-        <v>120.2</v>
+        <v>92.59</v>
       </c>
       <c r="D1181">
-        <v>24.17</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="1182" spans="1:4" x14ac:dyDescent="0.25">
@@ -17544,10 +17535,10 @@
         <v>9</v>
       </c>
       <c r="C1182">
-        <v>127</v>
+        <v>118.44</v>
       </c>
       <c r="D1182">
-        <v>6.8</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1183" spans="1:4" x14ac:dyDescent="0.25">
@@ -17558,10 +17549,10 @@
         <v>10</v>
       </c>
       <c r="C1183">
-        <v>128.4</v>
+        <v>118.44</v>
       </c>
       <c r="D1183">
-        <v>1.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1184" spans="1:4" x14ac:dyDescent="0.25">
@@ -17572,10 +17563,10 @@
         <v>11</v>
       </c>
       <c r="C1184">
-        <v>131.69999999999999</v>
+        <v>121.76</v>
       </c>
       <c r="D1184">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="1185" spans="1:4" x14ac:dyDescent="0.25">
@@ -17586,10 +17577,10 @@
         <v>12</v>
       </c>
       <c r="C1185">
-        <v>131.69999999999999</v>
+        <v>147.97999999999999</v>
       </c>
       <c r="D1185">
-        <v>0</v>
+        <v>26.22</v>
       </c>
     </row>
     <row r="1186" spans="1:4" x14ac:dyDescent="0.25">
@@ -17600,10 +17591,10 @@
         <v>13</v>
       </c>
       <c r="C1186">
-        <v>164.3</v>
+        <v>147.97999999999999</v>
       </c>
       <c r="D1186">
-        <v>32.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1187" spans="1:4" x14ac:dyDescent="0.25">
@@ -17614,10 +17605,10 @@
         <v>14</v>
       </c>
       <c r="C1187">
-        <v>165.18</v>
+        <v>147.97999999999999</v>
       </c>
       <c r="D1187">
-        <v>0.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1188" spans="1:4" x14ac:dyDescent="0.25">
@@ -17628,10 +17619,10 @@
         <v>5</v>
       </c>
       <c r="C1188">
-        <v>2.2000000000000002</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="D1188">
-        <v>2.2000000000000002</v>
+        <v>17.670000000000002</v>
       </c>
     </row>
     <row r="1189" spans="1:4" x14ac:dyDescent="0.25">
@@ -17642,10 +17633,10 @@
         <v>6</v>
       </c>
       <c r="C1189">
-        <v>62.33</v>
+        <v>58.16</v>
       </c>
       <c r="D1189">
-        <v>60.13</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="1190" spans="1:4" x14ac:dyDescent="0.25">
@@ -17656,10 +17647,10 @@
         <v>7</v>
       </c>
       <c r="C1190">
-        <v>85.4</v>
+        <v>62.86</v>
       </c>
       <c r="D1190">
-        <v>23.07</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="1191" spans="1:4" x14ac:dyDescent="0.25">
@@ -17670,10 +17661,10 @@
         <v>8</v>
       </c>
       <c r="C1191">
-        <v>92.59</v>
+        <v>66.599999999999994</v>
       </c>
       <c r="D1191">
-        <v>7.19</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="1192" spans="1:4" x14ac:dyDescent="0.25">
@@ -17684,10 +17675,10 @@
         <v>9</v>
       </c>
       <c r="C1192">
-        <v>118.44</v>
+        <v>88.8</v>
       </c>
       <c r="D1192">
-        <v>25.85</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="1193" spans="1:4" x14ac:dyDescent="0.25">
@@ -17698,7 +17689,7 @@
         <v>10</v>
       </c>
       <c r="C1193">
-        <v>118.44</v>
+        <v>88.8</v>
       </c>
       <c r="D1193">
         <v>0</v>
@@ -17712,10 +17703,10 @@
         <v>11</v>
       </c>
       <c r="C1194">
-        <v>121.76</v>
+        <v>92.6</v>
       </c>
       <c r="D1194">
-        <v>3.32</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="1195" spans="1:4" x14ac:dyDescent="0.25">
@@ -17726,10 +17717,10 @@
         <v>12</v>
       </c>
       <c r="C1195">
-        <v>147.97999999999999</v>
+        <v>92.6</v>
       </c>
       <c r="D1195">
-        <v>26.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1196" spans="1:4" x14ac:dyDescent="0.25">
@@ -17740,10 +17731,10 @@
         <v>13</v>
       </c>
       <c r="C1196">
-        <v>147.97999999999999</v>
+        <v>94.92</v>
       </c>
       <c r="D1196">
-        <v>0</v>
+        <v>2.3199999999999998</v>
       </c>
     </row>
     <row r="1197" spans="1:4" x14ac:dyDescent="0.25">
@@ -17754,10 +17745,10 @@
         <v>14</v>
       </c>
       <c r="C1197">
-        <v>147.97999999999999</v>
+        <v>129.9</v>
       </c>
       <c r="D1197">
-        <v>0</v>
+        <v>34.979999999999997</v>
       </c>
     </row>
     <row r="1198" spans="1:4" x14ac:dyDescent="0.25">
@@ -17768,10 +17759,10 @@
         <v>5</v>
       </c>
       <c r="C1198">
-        <v>17.670000000000002</v>
+        <v>0.8</v>
       </c>
       <c r="D1198">
-        <v>17.670000000000002</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="1199" spans="1:4" x14ac:dyDescent="0.25">
@@ -17782,10 +17773,10 @@
         <v>6</v>
       </c>
       <c r="C1199">
-        <v>58.16</v>
+        <v>21.49</v>
       </c>
       <c r="D1199">
-        <v>40.49</v>
+        <v>20.69</v>
       </c>
     </row>
     <row r="1200" spans="1:4" x14ac:dyDescent="0.25">
@@ -17796,10 +17787,10 @@
         <v>7</v>
       </c>
       <c r="C1200">
-        <v>62.86</v>
+        <v>74.14</v>
       </c>
       <c r="D1200">
-        <v>4.7</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="1201" spans="1:4" x14ac:dyDescent="0.25">
@@ -17810,10 +17801,10 @@
         <v>8</v>
       </c>
       <c r="C1201">
-        <v>66.599999999999994</v>
+        <v>85.62</v>
       </c>
       <c r="D1201">
-        <v>3.74</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="1202" spans="1:4" x14ac:dyDescent="0.25">
@@ -17824,10 +17815,10 @@
         <v>9</v>
       </c>
       <c r="C1202">
-        <v>88.8</v>
+        <v>101.7</v>
       </c>
       <c r="D1202">
-        <v>22.2</v>
+        <v>16.079999999999998</v>
       </c>
     </row>
     <row r="1203" spans="1:4" x14ac:dyDescent="0.25">
@@ -17838,10 +17829,10 @@
         <v>10</v>
       </c>
       <c r="C1203">
-        <v>88.8</v>
+        <v>107.78</v>
       </c>
       <c r="D1203">
-        <v>0</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="1204" spans="1:4" x14ac:dyDescent="0.25">
@@ -17852,10 +17843,10 @@
         <v>11</v>
       </c>
       <c r="C1204">
-        <v>92.6</v>
+        <v>111.08</v>
       </c>
       <c r="D1204">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="1205" spans="1:4" x14ac:dyDescent="0.25">
@@ -17866,7 +17857,7 @@
         <v>12</v>
       </c>
       <c r="C1205">
-        <v>92.6</v>
+        <v>111.08</v>
       </c>
       <c r="D1205">
         <v>0</v>
@@ -17880,10 +17871,10 @@
         <v>13</v>
       </c>
       <c r="C1206">
-        <v>94.92</v>
+        <v>112.9</v>
       </c>
       <c r="D1206">
-        <v>2.3199999999999998</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="1207" spans="1:4" x14ac:dyDescent="0.25">
@@ -17894,10 +17885,10 @@
         <v>14</v>
       </c>
       <c r="C1207">
-        <v>129.9</v>
+        <v>152.27000000000001</v>
       </c>
       <c r="D1207">
-        <v>34.979999999999997</v>
+        <v>39.369999999999997</v>
       </c>
     </row>
     <row r="1208" spans="1:4" x14ac:dyDescent="0.25">
@@ -17908,10 +17899,10 @@
         <v>5</v>
       </c>
       <c r="C1208">
-        <v>0.8</v>
+        <v>28.4</v>
       </c>
       <c r="D1208">
-        <v>0.8</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="1209" spans="1:4" x14ac:dyDescent="0.25">
@@ -17922,10 +17913,10 @@
         <v>6</v>
       </c>
       <c r="C1209">
-        <v>21.49</v>
+        <v>61.8</v>
       </c>
       <c r="D1209">
-        <v>20.69</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="1210" spans="1:4" x14ac:dyDescent="0.25">
@@ -17936,10 +17927,10 @@
         <v>7</v>
       </c>
       <c r="C1210">
-        <v>74.14</v>
+        <v>61.8</v>
       </c>
       <c r="D1210">
-        <v>52.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1211" spans="1:4" x14ac:dyDescent="0.25">
@@ -17950,10 +17941,10 @@
         <v>8</v>
       </c>
       <c r="C1211">
-        <v>85.62</v>
+        <v>61.8</v>
       </c>
       <c r="D1211">
-        <v>11.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1212" spans="1:4" x14ac:dyDescent="0.25">
@@ -17964,10 +17955,10 @@
         <v>9</v>
       </c>
       <c r="C1212">
-        <v>101.7</v>
+        <v>90.49</v>
       </c>
       <c r="D1212">
-        <v>16.079999999999998</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="1213" spans="1:4" x14ac:dyDescent="0.25">
@@ -17978,10 +17969,10 @@
         <v>10</v>
       </c>
       <c r="C1213">
-        <v>107.78</v>
+        <v>90.69</v>
       </c>
       <c r="D1213">
-        <v>6.08</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="1214" spans="1:4" x14ac:dyDescent="0.25">
@@ -17992,10 +17983,10 @@
         <v>11</v>
       </c>
       <c r="C1214">
-        <v>111.08</v>
+        <v>94.04</v>
       </c>
       <c r="D1214">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="1215" spans="1:4" x14ac:dyDescent="0.25">
@@ -18006,7 +17997,7 @@
         <v>12</v>
       </c>
       <c r="C1215">
-        <v>111.08</v>
+        <v>94.04</v>
       </c>
       <c r="D1215">
         <v>0</v>
@@ -18020,10 +18011,10 @@
         <v>13</v>
       </c>
       <c r="C1216">
-        <v>112.9</v>
+        <v>95.39</v>
       </c>
       <c r="D1216">
-        <v>1.82</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="1217" spans="1:4" x14ac:dyDescent="0.25">
@@ -18034,10 +18025,10 @@
         <v>14</v>
       </c>
       <c r="C1217">
-        <v>152.27000000000001</v>
+        <v>133.74</v>
       </c>
       <c r="D1217">
-        <v>39.369999999999997</v>
+        <v>38.35</v>
       </c>
     </row>
     <row r="1218" spans="1:4" x14ac:dyDescent="0.25">
@@ -18048,10 +18039,10 @@
         <v>5</v>
       </c>
       <c r="C1218">
-        <v>28.4</v>
+        <v>52.79</v>
       </c>
       <c r="D1218">
-        <v>28.4</v>
+        <v>52.79</v>
       </c>
     </row>
     <row r="1219" spans="1:4" x14ac:dyDescent="0.25">
@@ -18062,10 +18053,10 @@
         <v>6</v>
       </c>
       <c r="C1219">
-        <v>61.8</v>
+        <v>65.83</v>
       </c>
       <c r="D1219">
-        <v>33.4</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="1220" spans="1:4" x14ac:dyDescent="0.25">
@@ -18076,10 +18067,10 @@
         <v>7</v>
       </c>
       <c r="C1220">
-        <v>61.8</v>
+        <v>92.81</v>
       </c>
       <c r="D1220">
-        <v>0</v>
+        <v>26.98</v>
       </c>
     </row>
     <row r="1221" spans="1:4" x14ac:dyDescent="0.25">
@@ -18090,10 +18081,10 @@
         <v>8</v>
       </c>
       <c r="C1221">
-        <v>61.8</v>
+        <v>103.55</v>
       </c>
       <c r="D1221">
-        <v>0</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="1222" spans="1:4" x14ac:dyDescent="0.25">
@@ -18104,10 +18095,10 @@
         <v>9</v>
       </c>
       <c r="C1222">
-        <v>90.49</v>
+        <v>106.55</v>
       </c>
       <c r="D1222">
-        <v>28.69</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1223" spans="1:4" x14ac:dyDescent="0.25">
@@ -18118,10 +18109,10 @@
         <v>10</v>
       </c>
       <c r="C1223">
-        <v>90.69</v>
+        <v>106.55</v>
       </c>
       <c r="D1223">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1224" spans="1:4" x14ac:dyDescent="0.25">
@@ -18132,10 +18123,10 @@
         <v>11</v>
       </c>
       <c r="C1224">
-        <v>94.04</v>
+        <v>109.86</v>
       </c>
       <c r="D1224">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="1225" spans="1:4" x14ac:dyDescent="0.25">
@@ -18146,10 +18137,10 @@
         <v>12</v>
       </c>
       <c r="C1225">
-        <v>94.04</v>
+        <v>122.01</v>
       </c>
       <c r="D1225">
-        <v>0</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="1226" spans="1:4" x14ac:dyDescent="0.25">
@@ -18160,10 +18151,10 @@
         <v>13</v>
       </c>
       <c r="C1226">
-        <v>95.39</v>
+        <v>132.15</v>
       </c>
       <c r="D1226">
-        <v>1.35</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="1227" spans="1:4" x14ac:dyDescent="0.25">
@@ -18174,10 +18165,10 @@
         <v>14</v>
       </c>
       <c r="C1227">
-        <v>133.74</v>
+        <v>150.32</v>
       </c>
       <c r="D1227">
-        <v>38.35</v>
+        <v>18.170000000000002</v>
       </c>
     </row>
     <row r="1228" spans="1:4" x14ac:dyDescent="0.25">
@@ -18188,10 +18179,10 @@
         <v>5</v>
       </c>
       <c r="C1228">
-        <v>52.79</v>
+        <v>23.71</v>
       </c>
       <c r="D1228">
-        <v>52.79</v>
+        <v>23.71</v>
       </c>
     </row>
     <row r="1229" spans="1:4" x14ac:dyDescent="0.25">
@@ -18202,10 +18193,10 @@
         <v>6</v>
       </c>
       <c r="C1229">
-        <v>65.83</v>
+        <v>37.729999999999997</v>
       </c>
       <c r="D1229">
-        <v>13.04</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="1230" spans="1:4" x14ac:dyDescent="0.25">
@@ -18216,10 +18207,10 @@
         <v>7</v>
       </c>
       <c r="C1230">
-        <v>92.81</v>
+        <v>41.75</v>
       </c>
       <c r="D1230">
-        <v>26.98</v>
+        <v>4.0199999999999996</v>
       </c>
     </row>
     <row r="1231" spans="1:4" x14ac:dyDescent="0.25">
@@ -18230,10 +18221,10 @@
         <v>8</v>
       </c>
       <c r="C1231">
-        <v>103.55</v>
+        <v>77.569999999999993</v>
       </c>
       <c r="D1231">
-        <v>10.74</v>
+        <v>35.82</v>
       </c>
     </row>
     <row r="1232" spans="1:4" x14ac:dyDescent="0.25">
@@ -18244,10 +18235,10 @@
         <v>9</v>
       </c>
       <c r="C1232">
-        <v>106.55</v>
+        <v>104.91</v>
       </c>
       <c r="D1232">
-        <v>3</v>
+        <v>27.34</v>
       </c>
     </row>
     <row r="1233" spans="1:4" x14ac:dyDescent="0.25">
@@ -18258,7 +18249,7 @@
         <v>10</v>
       </c>
       <c r="C1233">
-        <v>106.55</v>
+        <v>104.91</v>
       </c>
       <c r="D1233">
         <v>0</v>
@@ -18272,10 +18263,10 @@
         <v>11</v>
       </c>
       <c r="C1234">
-        <v>109.86</v>
+        <v>108.11</v>
       </c>
       <c r="D1234">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="1235" spans="1:4" x14ac:dyDescent="0.25">
@@ -18286,10 +18277,10 @@
         <v>12</v>
       </c>
       <c r="C1235">
-        <v>122.01</v>
+        <v>108.11</v>
       </c>
       <c r="D1235">
-        <v>12.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1236" spans="1:4" x14ac:dyDescent="0.25">
@@ -18300,10 +18291,10 @@
         <v>13</v>
       </c>
       <c r="C1236">
-        <v>132.15</v>
+        <v>108.51</v>
       </c>
       <c r="D1236">
-        <v>10.14</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="1237" spans="1:4" x14ac:dyDescent="0.25">
@@ -18314,10 +18305,10 @@
         <v>14</v>
       </c>
       <c r="C1237">
-        <v>150.32</v>
+        <v>150.02000000000001</v>
       </c>
       <c r="D1237">
-        <v>18.170000000000002</v>
+        <v>41.51</v>
       </c>
     </row>
     <row r="1238" spans="1:4" x14ac:dyDescent="0.25">
@@ -18328,10 +18319,10 @@
         <v>5</v>
       </c>
       <c r="C1238">
-        <v>23.71</v>
+        <v>58.5</v>
       </c>
       <c r="D1238">
-        <v>23.71</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="1239" spans="1:4" x14ac:dyDescent="0.25">
@@ -18342,10 +18333,10 @@
         <v>6</v>
       </c>
       <c r="C1239">
-        <v>37.729999999999997</v>
+        <v>58.5</v>
       </c>
       <c r="D1239">
-        <v>14.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1240" spans="1:4" x14ac:dyDescent="0.25">
@@ -18356,10 +18347,10 @@
         <v>7</v>
       </c>
       <c r="C1240">
-        <v>41.75</v>
+        <v>65.55</v>
       </c>
       <c r="D1240">
-        <v>4.0199999999999996</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="1241" spans="1:4" x14ac:dyDescent="0.25">
@@ -18370,10 +18361,10 @@
         <v>8</v>
       </c>
       <c r="C1241">
-        <v>77.569999999999993</v>
+        <v>96.42</v>
       </c>
       <c r="D1241">
-        <v>35.82</v>
+        <v>30.87</v>
       </c>
     </row>
     <row r="1242" spans="1:4" x14ac:dyDescent="0.25">
@@ -18384,10 +18375,10 @@
         <v>9</v>
       </c>
       <c r="C1242">
-        <v>104.91</v>
+        <v>124.87</v>
       </c>
       <c r="D1242">
-        <v>27.34</v>
+        <v>28.45</v>
       </c>
     </row>
     <row r="1243" spans="1:4" x14ac:dyDescent="0.25">
@@ -18398,7 +18389,7 @@
         <v>10</v>
       </c>
       <c r="C1243">
-        <v>104.91</v>
+        <v>124.87</v>
       </c>
       <c r="D1243">
         <v>0</v>
@@ -18412,10 +18403,10 @@
         <v>11</v>
       </c>
       <c r="C1244">
-        <v>108.11</v>
+        <v>127.94</v>
       </c>
       <c r="D1244">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="1245" spans="1:4" x14ac:dyDescent="0.25">
@@ -18426,10 +18417,10 @@
         <v>12</v>
       </c>
       <c r="C1245">
-        <v>108.11</v>
+        <v>168.95</v>
       </c>
       <c r="D1245">
-        <v>0</v>
+        <v>41.01</v>
       </c>
     </row>
     <row r="1246" spans="1:4" x14ac:dyDescent="0.25">
@@ -18440,10 +18431,10 @@
         <v>13</v>
       </c>
       <c r="C1246">
-        <v>108.51</v>
+        <v>168.95</v>
       </c>
       <c r="D1246">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1247" spans="1:4" x14ac:dyDescent="0.25">
@@ -18454,10 +18445,10 @@
         <v>14</v>
       </c>
       <c r="C1247">
-        <v>150.02000000000001</v>
+        <v>168.95</v>
       </c>
       <c r="D1247">
-        <v>41.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1248" spans="1:4" x14ac:dyDescent="0.25">
@@ -18468,10 +18459,10 @@
         <v>5</v>
       </c>
       <c r="C1248">
-        <v>58.5</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="D1248">
-        <v>58.5</v>
+        <v>8.5299999999999994</v>
       </c>
     </row>
     <row r="1249" spans="1:4" x14ac:dyDescent="0.25">
@@ -18482,10 +18473,10 @@
         <v>6</v>
       </c>
       <c r="C1249">
-        <v>58.5</v>
+        <v>25.83</v>
       </c>
       <c r="D1249">
-        <v>0</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="1250" spans="1:4" x14ac:dyDescent="0.25">
@@ -18496,10 +18487,10 @@
         <v>7</v>
       </c>
       <c r="C1250">
-        <v>65.55</v>
+        <v>103.14</v>
       </c>
       <c r="D1250">
-        <v>7.05</v>
+        <v>77.31</v>
       </c>
     </row>
     <row r="1251" spans="1:4" x14ac:dyDescent="0.25">
@@ -18510,10 +18501,10 @@
         <v>8</v>
       </c>
       <c r="C1251">
-        <v>96.42</v>
+        <v>110.07</v>
       </c>
       <c r="D1251">
-        <v>30.87</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="1252" spans="1:4" x14ac:dyDescent="0.25">
@@ -18524,10 +18515,10 @@
         <v>9</v>
       </c>
       <c r="C1252">
-        <v>124.87</v>
+        <v>133.21</v>
       </c>
       <c r="D1252">
-        <v>28.45</v>
+        <v>23.14</v>
       </c>
     </row>
     <row r="1253" spans="1:4" x14ac:dyDescent="0.25">
@@ -18538,10 +18529,10 @@
         <v>10</v>
       </c>
       <c r="C1253">
-        <v>124.87</v>
+        <v>134.19</v>
       </c>
       <c r="D1253">
-        <v>0</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="1254" spans="1:4" x14ac:dyDescent="0.25">
@@ -18552,10 +18543,10 @@
         <v>11</v>
       </c>
       <c r="C1254">
-        <v>127.94</v>
+        <v>137.27000000000001</v>
       </c>
       <c r="D1254">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="1255" spans="1:4" x14ac:dyDescent="0.25">
@@ -18566,10 +18557,10 @@
         <v>12</v>
       </c>
       <c r="C1255">
-        <v>168.95</v>
+        <v>137.27000000000001</v>
       </c>
       <c r="D1255">
-        <v>41.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1256" spans="1:4" x14ac:dyDescent="0.25">
@@ -18580,10 +18571,10 @@
         <v>13</v>
       </c>
       <c r="C1256">
-        <v>168.95</v>
+        <v>165.59</v>
       </c>
       <c r="D1256">
-        <v>0</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="1257" spans="1:4" x14ac:dyDescent="0.25">
@@ -18594,10 +18585,10 @@
         <v>14</v>
       </c>
       <c r="C1257">
-        <v>168.95</v>
+        <v>177.49</v>
       </c>
       <c r="D1257">
-        <v>0</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="1258" spans="1:4" x14ac:dyDescent="0.25">
@@ -18608,10 +18599,10 @@
         <v>5</v>
       </c>
       <c r="C1258">
-        <v>8.5299999999999994</v>
+        <v>7.06</v>
       </c>
       <c r="D1258">
-        <v>8.5299999999999994</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="1259" spans="1:4" x14ac:dyDescent="0.25">
@@ -18622,10 +18613,10 @@
         <v>6</v>
       </c>
       <c r="C1259">
-        <v>25.83</v>
+        <v>41.88</v>
       </c>
       <c r="D1259">
-        <v>17.3</v>
+        <v>34.82</v>
       </c>
     </row>
     <row r="1260" spans="1:4" x14ac:dyDescent="0.25">
@@ -18636,10 +18627,10 @@
         <v>7</v>
       </c>
       <c r="C1260">
-        <v>103.14</v>
+        <v>95.85</v>
       </c>
       <c r="D1260">
-        <v>77.31</v>
+        <v>53.97</v>
       </c>
     </row>
     <row r="1261" spans="1:4" x14ac:dyDescent="0.25">
@@ -18650,10 +18641,10 @@
         <v>8</v>
       </c>
       <c r="C1261">
-        <v>110.07</v>
+        <v>125.22</v>
       </c>
       <c r="D1261">
-        <v>6.93</v>
+        <v>29.37</v>
       </c>
     </row>
     <row r="1262" spans="1:4" x14ac:dyDescent="0.25">
@@ -18664,10 +18655,10 @@
         <v>9</v>
       </c>
       <c r="C1262">
-        <v>133.21</v>
+        <v>155.22999999999999</v>
       </c>
       <c r="D1262">
-        <v>23.14</v>
+        <v>30.01</v>
       </c>
     </row>
     <row r="1263" spans="1:4" x14ac:dyDescent="0.25">
@@ -18678,10 +18669,10 @@
         <v>10</v>
       </c>
       <c r="C1263">
-        <v>134.19</v>
+        <v>155.22999999999999</v>
       </c>
       <c r="D1263">
-        <v>0.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1264" spans="1:4" x14ac:dyDescent="0.25">
@@ -18692,10 +18683,10 @@
         <v>11</v>
       </c>
       <c r="C1264">
-        <v>137.27000000000001</v>
+        <v>158.59</v>
       </c>
       <c r="D1264">
-        <v>3.08</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="1265" spans="1:4" x14ac:dyDescent="0.25">
@@ -18706,10 +18697,10 @@
         <v>12</v>
       </c>
       <c r="C1265">
-        <v>137.27000000000001</v>
+        <v>202.04</v>
       </c>
       <c r="D1265">
-        <v>0</v>
+        <v>43.45</v>
       </c>
     </row>
     <row r="1266" spans="1:4" x14ac:dyDescent="0.25">
@@ -18720,10 +18711,10 @@
         <v>13</v>
       </c>
       <c r="C1266">
-        <v>165.59</v>
+        <v>202.04</v>
       </c>
       <c r="D1266">
-        <v>28.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1267" spans="1:4" x14ac:dyDescent="0.25">
@@ -18734,10 +18725,10 @@
         <v>14</v>
       </c>
       <c r="C1267">
-        <v>177.49</v>
+        <v>202.04</v>
       </c>
       <c r="D1267">
-        <v>11.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1268" spans="1:4" x14ac:dyDescent="0.25">
@@ -18748,10 +18739,10 @@
         <v>5</v>
       </c>
       <c r="C1268">
-        <v>7.06</v>
+        <v>3.73</v>
       </c>
       <c r="D1268">
-        <v>7.06</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="1269" spans="1:4" x14ac:dyDescent="0.25">
@@ -18762,10 +18753,10 @@
         <v>6</v>
       </c>
       <c r="C1269">
-        <v>41.88</v>
+        <v>93.28</v>
       </c>
       <c r="D1269">
-        <v>34.82</v>
+        <v>89.55</v>
       </c>
     </row>
     <row r="1270" spans="1:4" x14ac:dyDescent="0.25">
@@ -18776,10 +18767,10 @@
         <v>7</v>
       </c>
       <c r="C1270">
-        <v>95.85</v>
+        <v>160.80000000000001</v>
       </c>
       <c r="D1270">
-        <v>53.97</v>
+        <v>67.52</v>
       </c>
     </row>
     <row r="1271" spans="1:4" x14ac:dyDescent="0.25">
@@ -18790,10 +18781,10 @@
         <v>8</v>
       </c>
       <c r="C1271">
-        <v>125.22</v>
+        <v>165.05</v>
       </c>
       <c r="D1271">
-        <v>29.37</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="1272" spans="1:4" x14ac:dyDescent="0.25">
@@ -18804,10 +18795,10 @@
         <v>9</v>
       </c>
       <c r="C1272">
-        <v>155.22999999999999</v>
+        <v>184.48</v>
       </c>
       <c r="D1272">
-        <v>30.01</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="1273" spans="1:4" x14ac:dyDescent="0.25">
@@ -18818,10 +18809,10 @@
         <v>10</v>
       </c>
       <c r="C1273">
-        <v>155.22999999999999</v>
+        <v>188.27</v>
       </c>
       <c r="D1273">
-        <v>0</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="1274" spans="1:4" x14ac:dyDescent="0.25">
@@ -18832,10 +18823,10 @@
         <v>11</v>
       </c>
       <c r="C1274">
-        <v>158.59</v>
+        <v>191.19</v>
       </c>
       <c r="D1274">
-        <v>3.36</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="1275" spans="1:4" x14ac:dyDescent="0.25">
@@ -18846,10 +18837,10 @@
         <v>12</v>
       </c>
       <c r="C1275">
-        <v>202.04</v>
+        <v>191.19</v>
       </c>
       <c r="D1275">
-        <v>43.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1276" spans="1:4" x14ac:dyDescent="0.25">
@@ -18860,10 +18851,10 @@
         <v>13</v>
       </c>
       <c r="C1276">
-        <v>202.04</v>
+        <v>202.65</v>
       </c>
       <c r="D1276">
-        <v>0</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="1277" spans="1:4" x14ac:dyDescent="0.25">
@@ -18874,10 +18865,10 @@
         <v>14</v>
       </c>
       <c r="C1277">
-        <v>202.04</v>
+        <v>232.92</v>
       </c>
       <c r="D1277">
-        <v>0</v>
+        <v>30.27</v>
       </c>
     </row>
     <row r="1278" spans="1:4" x14ac:dyDescent="0.25">
@@ -18888,10 +18879,10 @@
         <v>5</v>
       </c>
       <c r="C1278">
-        <v>3.73</v>
+        <v>0.95</v>
       </c>
       <c r="D1278">
-        <v>3.73</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="1279" spans="1:4" x14ac:dyDescent="0.25">
@@ -18902,10 +18893,10 @@
         <v>6</v>
       </c>
       <c r="C1279">
-        <v>93.28</v>
+        <v>60</v>
       </c>
       <c r="D1279">
-        <v>89.55</v>
+        <v>59.05</v>
       </c>
     </row>
     <row r="1280" spans="1:4" x14ac:dyDescent="0.25">
@@ -18916,10 +18907,10 @@
         <v>7</v>
       </c>
       <c r="C1280">
-        <v>160.80000000000001</v>
+        <v>64.739999999999995</v>
       </c>
       <c r="D1280">
-        <v>67.52</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="1281" spans="1:4" x14ac:dyDescent="0.25">
@@ -18930,10 +18921,10 @@
         <v>8</v>
       </c>
       <c r="C1281">
-        <v>165.05</v>
+        <v>83.59</v>
       </c>
       <c r="D1281">
-        <v>4.25</v>
+        <v>18.850000000000001</v>
       </c>
     </row>
     <row r="1282" spans="1:4" x14ac:dyDescent="0.25">
@@ -18944,10 +18935,10 @@
         <v>9</v>
       </c>
       <c r="C1282">
-        <v>184.48</v>
+        <v>101.02</v>
       </c>
       <c r="D1282">
-        <v>19.43</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="1283" spans="1:4" x14ac:dyDescent="0.25">
@@ -18958,10 +18949,10 @@
         <v>10</v>
       </c>
       <c r="C1283">
-        <v>188.27</v>
+        <v>103.15</v>
       </c>
       <c r="D1283">
-        <v>3.79</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="1284" spans="1:4" x14ac:dyDescent="0.25">
@@ -18972,10 +18963,10 @@
         <v>11</v>
       </c>
       <c r="C1284">
-        <v>191.19</v>
+        <v>106.61</v>
       </c>
       <c r="D1284">
-        <v>2.92</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="1285" spans="1:4" x14ac:dyDescent="0.25">
@@ -18986,7 +18977,7 @@
         <v>12</v>
       </c>
       <c r="C1285">
-        <v>191.19</v>
+        <v>106.61</v>
       </c>
       <c r="D1285">
         <v>0</v>
@@ -19000,10 +18991,10 @@
         <v>13</v>
       </c>
       <c r="C1286">
-        <v>202.65</v>
+        <v>109</v>
       </c>
       <c r="D1286">
-        <v>11.46</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="1287" spans="1:4" x14ac:dyDescent="0.25">
@@ -19014,10 +19005,10 @@
         <v>14</v>
       </c>
       <c r="C1287">
-        <v>232.92</v>
+        <v>141.06</v>
       </c>
       <c r="D1287">
-        <v>30.27</v>
+        <v>32.06</v>
       </c>
     </row>
     <row r="1288" spans="1:4" x14ac:dyDescent="0.25">
@@ -19028,10 +19019,10 @@
         <v>5</v>
       </c>
       <c r="C1288">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="D1288">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="1289" spans="1:4" x14ac:dyDescent="0.25">
@@ -19042,10 +19033,10 @@
         <v>6</v>
       </c>
       <c r="C1289">
-        <v>60</v>
+        <v>38.49</v>
       </c>
       <c r="D1289">
-        <v>59.05</v>
+        <v>37.69</v>
       </c>
     </row>
     <row r="1290" spans="1:4" x14ac:dyDescent="0.25">
@@ -19056,10 +19047,10 @@
         <v>7</v>
       </c>
       <c r="C1290">
-        <v>64.739999999999995</v>
+        <v>65.73</v>
       </c>
       <c r="D1290">
-        <v>4.74</v>
+        <v>27.24</v>
       </c>
     </row>
     <row r="1291" spans="1:4" x14ac:dyDescent="0.25">
@@ -19070,10 +19061,10 @@
         <v>8</v>
       </c>
       <c r="C1291">
-        <v>83.59</v>
+        <v>67.180000000000007</v>
       </c>
       <c r="D1291">
-        <v>18.850000000000001</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="1292" spans="1:4" x14ac:dyDescent="0.25">
@@ -19084,10 +19075,10 @@
         <v>9</v>
       </c>
       <c r="C1292">
-        <v>101.02</v>
+        <v>101.75</v>
       </c>
       <c r="D1292">
-        <v>17.43</v>
+        <v>34.57</v>
       </c>
     </row>
     <row r="1293" spans="1:4" x14ac:dyDescent="0.25">
@@ -19098,10 +19089,10 @@
         <v>10</v>
       </c>
       <c r="C1293">
-        <v>103.15</v>
+        <v>101.85</v>
       </c>
       <c r="D1293">
-        <v>2.13</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="1294" spans="1:4" x14ac:dyDescent="0.25">
@@ -19112,10 +19103,10 @@
         <v>11</v>
       </c>
       <c r="C1294">
-        <v>106.61</v>
+        <v>105.2</v>
       </c>
       <c r="D1294">
-        <v>3.46</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="1295" spans="1:4" x14ac:dyDescent="0.25">
@@ -19126,10 +19117,10 @@
         <v>12</v>
       </c>
       <c r="C1295">
-        <v>106.61</v>
+        <v>139.02000000000001</v>
       </c>
       <c r="D1295">
-        <v>0</v>
+        <v>33.82</v>
       </c>
     </row>
     <row r="1296" spans="1:4" x14ac:dyDescent="0.25">
@@ -19140,10 +19131,10 @@
         <v>13</v>
       </c>
       <c r="C1296">
-        <v>109</v>
+        <v>139.02000000000001</v>
       </c>
       <c r="D1296">
-        <v>2.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1297" spans="1:4" x14ac:dyDescent="0.25">
@@ -19154,10 +19145,10 @@
         <v>14</v>
       </c>
       <c r="C1297">
-        <v>141.06</v>
+        <v>139.02000000000001</v>
       </c>
       <c r="D1297">
-        <v>32.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1298" spans="1:4" x14ac:dyDescent="0.25">
@@ -19168,10 +19159,10 @@
         <v>5</v>
       </c>
       <c r="C1298">
-        <v>0.8</v>
+        <v>18.53</v>
       </c>
       <c r="D1298">
-        <v>0.8</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="1299" spans="1:4" x14ac:dyDescent="0.25">
@@ -19182,10 +19173,10 @@
         <v>6</v>
       </c>
       <c r="C1299">
-        <v>38.49</v>
+        <v>29.82</v>
       </c>
       <c r="D1299">
-        <v>37.69</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="1300" spans="1:4" x14ac:dyDescent="0.25">
@@ -19196,10 +19187,10 @@
         <v>7</v>
       </c>
       <c r="C1300">
-        <v>65.73</v>
+        <v>59.3</v>
       </c>
       <c r="D1300">
-        <v>27.24</v>
+        <v>29.48</v>
       </c>
     </row>
     <row r="1301" spans="1:4" x14ac:dyDescent="0.25">
@@ -19210,10 +19201,10 @@
         <v>8</v>
       </c>
       <c r="C1301">
-        <v>67.180000000000007</v>
+        <v>62</v>
       </c>
       <c r="D1301">
-        <v>1.45</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="1302" spans="1:4" x14ac:dyDescent="0.25">
@@ -19224,10 +19215,10 @@
         <v>9</v>
       </c>
       <c r="C1302">
-        <v>101.75</v>
+        <v>94.11</v>
       </c>
       <c r="D1302">
-        <v>34.57</v>
+        <v>32.11</v>
       </c>
     </row>
     <row r="1303" spans="1:4" x14ac:dyDescent="0.25">
@@ -19238,10 +19229,10 @@
         <v>10</v>
       </c>
       <c r="C1303">
-        <v>101.85</v>
+        <v>94.11</v>
       </c>
       <c r="D1303">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1304" spans="1:4" x14ac:dyDescent="0.25">
@@ -19252,10 +19243,10 @@
         <v>11</v>
       </c>
       <c r="C1304">
-        <v>105.2</v>
+        <v>97.71</v>
       </c>
       <c r="D1304">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="1305" spans="1:4" x14ac:dyDescent="0.25">
@@ -19266,10 +19257,10 @@
         <v>12</v>
       </c>
       <c r="C1305">
-        <v>139.02000000000001</v>
+        <v>137.54</v>
       </c>
       <c r="D1305">
-        <v>33.82</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="1306" spans="1:4" x14ac:dyDescent="0.25">
@@ -19280,7 +19271,7 @@
         <v>13</v>
       </c>
       <c r="C1306">
-        <v>139.02000000000001</v>
+        <v>137.54</v>
       </c>
       <c r="D1306">
         <v>0</v>
@@ -19294,7 +19285,7 @@
         <v>14</v>
       </c>
       <c r="C1307">
-        <v>139.02000000000001</v>
+        <v>137.54</v>
       </c>
       <c r="D1307">
         <v>0</v>
@@ -19308,10 +19299,10 @@
         <v>5</v>
       </c>
       <c r="C1308">
-        <v>18.53</v>
+        <v>23.91</v>
       </c>
       <c r="D1308">
-        <v>18.53</v>
+        <v>23.91</v>
       </c>
     </row>
     <row r="1309" spans="1:4" x14ac:dyDescent="0.25">
@@ -19322,10 +19313,10 @@
         <v>6</v>
       </c>
       <c r="C1309">
-        <v>29.82</v>
+        <v>60.62</v>
       </c>
       <c r="D1309">
-        <v>11.29</v>
+        <v>36.71</v>
       </c>
     </row>
     <row r="1310" spans="1:4" x14ac:dyDescent="0.25">
@@ -19336,10 +19327,10 @@
         <v>7</v>
       </c>
       <c r="C1310">
-        <v>59.3</v>
+        <v>60.62</v>
       </c>
       <c r="D1310">
-        <v>29.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1311" spans="1:4" x14ac:dyDescent="0.25">
@@ -19350,10 +19341,10 @@
         <v>8</v>
       </c>
       <c r="C1311">
-        <v>62</v>
+        <v>60.62</v>
       </c>
       <c r="D1311">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1312" spans="1:4" x14ac:dyDescent="0.25">
@@ -19364,10 +19355,10 @@
         <v>9</v>
       </c>
       <c r="C1312">
-        <v>94.11</v>
+        <v>90.56</v>
       </c>
       <c r="D1312">
-        <v>32.11</v>
+        <v>29.94</v>
       </c>
     </row>
     <row r="1313" spans="1:4" x14ac:dyDescent="0.25">
@@ -19378,7 +19369,7 @@
         <v>10</v>
       </c>
       <c r="C1313">
-        <v>94.11</v>
+        <v>90.56</v>
       </c>
       <c r="D1313">
         <v>0</v>
@@ -19392,10 +19383,10 @@
         <v>11</v>
       </c>
       <c r="C1314">
-        <v>97.71</v>
+        <v>99.91</v>
       </c>
       <c r="D1314">
-        <v>3.6</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="1315" spans="1:4" x14ac:dyDescent="0.25">
@@ -19406,10 +19397,10 @@
         <v>12</v>
       </c>
       <c r="C1315">
-        <v>137.54</v>
+        <v>102.33</v>
       </c>
       <c r="D1315">
-        <v>39.83</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="1316" spans="1:4" x14ac:dyDescent="0.25">
@@ -19420,10 +19411,10 @@
         <v>13</v>
       </c>
       <c r="C1316">
-        <v>137.54</v>
+        <v>102.53</v>
       </c>
       <c r="D1316">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="1317" spans="1:4" x14ac:dyDescent="0.25">
@@ -19434,10 +19425,10 @@
         <v>14</v>
       </c>
       <c r="C1317">
-        <v>137.54</v>
+        <v>139.05000000000001</v>
       </c>
       <c r="D1317">
-        <v>0</v>
+        <v>36.520000000000003</v>
       </c>
     </row>
     <row r="1318" spans="1:4" x14ac:dyDescent="0.25">
@@ -19448,10 +19439,10 @@
         <v>5</v>
       </c>
       <c r="C1318">
-        <v>23.91</v>
+        <v>9.76</v>
       </c>
       <c r="D1318">
-        <v>23.91</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="1319" spans="1:4" x14ac:dyDescent="0.25">
@@ -19462,10 +19453,10 @@
         <v>6</v>
       </c>
       <c r="C1319">
-        <v>60.62</v>
+        <v>21.99</v>
       </c>
       <c r="D1319">
-        <v>36.71</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="1320" spans="1:4" x14ac:dyDescent="0.25">
@@ -19476,10 +19467,10 @@
         <v>7</v>
       </c>
       <c r="C1320">
-        <v>60.62</v>
+        <v>27.22</v>
       </c>
       <c r="D1320">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="1321" spans="1:4" x14ac:dyDescent="0.25">
@@ -19490,10 +19481,10 @@
         <v>8</v>
       </c>
       <c r="C1321">
-        <v>60.62</v>
+        <v>27.72</v>
       </c>
       <c r="D1321">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1322" spans="1:4" x14ac:dyDescent="0.25">
@@ -19504,10 +19495,10 @@
         <v>9</v>
       </c>
       <c r="C1322">
-        <v>90.56</v>
+        <v>55.67</v>
       </c>
       <c r="D1322">
-        <v>29.94</v>
+        <v>27.95</v>
       </c>
     </row>
     <row r="1323" spans="1:4" x14ac:dyDescent="0.25">
@@ -19518,7 +19509,7 @@
         <v>10</v>
       </c>
       <c r="C1323">
-        <v>90.56</v>
+        <v>55.67</v>
       </c>
       <c r="D1323">
         <v>0</v>
@@ -19532,10 +19523,10 @@
         <v>11</v>
       </c>
       <c r="C1324">
-        <v>99.91</v>
+        <v>58.86</v>
       </c>
       <c r="D1324">
-        <v>9.35</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="1325" spans="1:4" x14ac:dyDescent="0.25">
@@ -19546,10 +19537,10 @@
         <v>12</v>
       </c>
       <c r="C1325">
-        <v>102.33</v>
+        <v>98.18</v>
       </c>
       <c r="D1325">
-        <v>2.42</v>
+        <v>39.32</v>
       </c>
     </row>
     <row r="1326" spans="1:4" x14ac:dyDescent="0.25">
@@ -19560,10 +19551,10 @@
         <v>13</v>
       </c>
       <c r="C1326">
-        <v>102.53</v>
+        <v>98.18</v>
       </c>
       <c r="D1326">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1327" spans="1:4" x14ac:dyDescent="0.25">
@@ -19574,10 +19565,10 @@
         <v>14</v>
       </c>
       <c r="C1327">
-        <v>139.05000000000001</v>
+        <v>98.18</v>
       </c>
       <c r="D1327">
-        <v>36.520000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1328" spans="1:4" x14ac:dyDescent="0.25">
@@ -19588,10 +19579,10 @@
         <v>5</v>
       </c>
       <c r="C1328">
-        <v>9.76</v>
+        <v>42.07</v>
       </c>
       <c r="D1328">
-        <v>9.76</v>
+        <v>42.07</v>
       </c>
     </row>
     <row r="1329" spans="1:4" x14ac:dyDescent="0.25">
@@ -19602,10 +19593,10 @@
         <v>6</v>
       </c>
       <c r="C1329">
-        <v>21.99</v>
+        <v>42.07</v>
       </c>
       <c r="D1329">
-        <v>12.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1330" spans="1:4" x14ac:dyDescent="0.25">
@@ -19616,10 +19607,10 @@
         <v>7</v>
       </c>
       <c r="C1330">
-        <v>27.22</v>
+        <v>70.760000000000005</v>
       </c>
       <c r="D1330">
-        <v>5.23</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="1331" spans="1:4" x14ac:dyDescent="0.25">
@@ -19630,10 +19621,10 @@
         <v>8</v>
       </c>
       <c r="C1331">
-        <v>27.72</v>
+        <v>95.74</v>
       </c>
       <c r="D1331">
-        <v>0.5</v>
+        <v>24.98</v>
       </c>
     </row>
     <row r="1332" spans="1:4" x14ac:dyDescent="0.25">
@@ -19644,10 +19635,10 @@
         <v>9</v>
       </c>
       <c r="C1332">
-        <v>55.67</v>
+        <v>98.94</v>
       </c>
       <c r="D1332">
-        <v>27.95</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="1333" spans="1:4" x14ac:dyDescent="0.25">
@@ -19658,7 +19649,7 @@
         <v>10</v>
       </c>
       <c r="C1333">
-        <v>55.67</v>
+        <v>98.94</v>
       </c>
       <c r="D1333">
         <v>0</v>
@@ -19672,10 +19663,10 @@
         <v>11</v>
       </c>
       <c r="C1334">
-        <v>58.86</v>
+        <v>102.31</v>
       </c>
       <c r="D1334">
-        <v>3.19</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="1335" spans="1:4" x14ac:dyDescent="0.25">
@@ -19686,10 +19677,10 @@
         <v>12</v>
       </c>
       <c r="C1335">
-        <v>98.18</v>
+        <v>102.31</v>
       </c>
       <c r="D1335">
-        <v>39.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1336" spans="1:4" x14ac:dyDescent="0.25">
@@ -19700,10 +19691,10 @@
         <v>13</v>
       </c>
       <c r="C1336">
-        <v>98.18</v>
+        <v>104.74</v>
       </c>
       <c r="D1336">
-        <v>0</v>
+        <v>2.4300000000000002</v>
       </c>
     </row>
     <row r="1337" spans="1:4" x14ac:dyDescent="0.25">
@@ -19714,10 +19705,10 @@
         <v>14</v>
       </c>
       <c r="C1337">
-        <v>98.18</v>
+        <v>142.76</v>
       </c>
       <c r="D1337">
-        <v>0</v>
+        <v>38.020000000000003</v>
       </c>
     </row>
     <row r="1338" spans="1:4" x14ac:dyDescent="0.25">
@@ -19728,10 +19719,10 @@
         <v>5</v>
       </c>
       <c r="C1338">
-        <v>42.07</v>
+        <v>73.5</v>
       </c>
       <c r="D1338">
-        <v>42.07</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="1339" spans="1:4" x14ac:dyDescent="0.25">
@@ -19742,7 +19733,7 @@
         <v>6</v>
       </c>
       <c r="C1339">
-        <v>42.07</v>
+        <v>73.5</v>
       </c>
       <c r="D1339">
         <v>0</v>
@@ -19756,10 +19747,10 @@
         <v>7</v>
       </c>
       <c r="C1340">
-        <v>70.760000000000005</v>
+        <v>77.75</v>
       </c>
       <c r="D1340">
-        <v>28.69</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="1341" spans="1:4" x14ac:dyDescent="0.25">
@@ -19770,10 +19761,10 @@
         <v>8</v>
       </c>
       <c r="C1341">
-        <v>95.74</v>
+        <v>78.55</v>
       </c>
       <c r="D1341">
-        <v>24.98</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="1342" spans="1:4" x14ac:dyDescent="0.25">
@@ -19784,10 +19775,10 @@
         <v>9</v>
       </c>
       <c r="C1342">
-        <v>98.94</v>
+        <v>107.51</v>
       </c>
       <c r="D1342">
-        <v>3.2</v>
+        <v>28.96</v>
       </c>
     </row>
     <row r="1343" spans="1:4" x14ac:dyDescent="0.25">
@@ -19798,7 +19789,7 @@
         <v>10</v>
       </c>
       <c r="C1343">
-        <v>98.94</v>
+        <v>107.51</v>
       </c>
       <c r="D1343">
         <v>0</v>
@@ -19812,10 +19803,10 @@
         <v>11</v>
       </c>
       <c r="C1344">
-        <v>102.31</v>
+        <v>110.81</v>
       </c>
       <c r="D1344">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="1345" spans="1:4" x14ac:dyDescent="0.25">
@@ -19826,10 +19817,10 @@
         <v>12</v>
       </c>
       <c r="C1345">
-        <v>102.31</v>
+        <v>150.11000000000001</v>
       </c>
       <c r="D1345">
-        <v>0</v>
+        <v>39.299999999999997</v>
       </c>
     </row>
     <row r="1346" spans="1:4" x14ac:dyDescent="0.25">
@@ -19840,10 +19831,10 @@
         <v>13</v>
       </c>
       <c r="C1346">
-        <v>104.74</v>
+        <v>150.11000000000001</v>
       </c>
       <c r="D1346">
-        <v>2.4300000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1347" spans="1:4" x14ac:dyDescent="0.25">
@@ -19854,10 +19845,10 @@
         <v>14</v>
       </c>
       <c r="C1347">
-        <v>142.76</v>
+        <v>150.11000000000001</v>
       </c>
       <c r="D1347">
-        <v>38.020000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1348" spans="1:4" x14ac:dyDescent="0.25">
@@ -19868,10 +19859,10 @@
         <v>5</v>
       </c>
       <c r="C1348">
-        <v>73.5</v>
+        <v>30.77</v>
       </c>
       <c r="D1348">
-        <v>73.5</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="1349" spans="1:4" x14ac:dyDescent="0.25">
@@ -19882,10 +19873,10 @@
         <v>6</v>
       </c>
       <c r="C1349">
-        <v>73.5</v>
+        <v>41</v>
       </c>
       <c r="D1349">
-        <v>0</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="1350" spans="1:4" x14ac:dyDescent="0.25">
@@ -19896,10 +19887,10 @@
         <v>7</v>
       </c>
       <c r="C1350">
-        <v>77.75</v>
+        <v>81.8</v>
       </c>
       <c r="D1350">
-        <v>4.25</v>
+        <v>40.799999999999997</v>
       </c>
     </row>
     <row r="1351" spans="1:4" x14ac:dyDescent="0.25">
@@ -19910,10 +19901,10 @@
         <v>8</v>
       </c>
       <c r="C1351">
-        <v>78.55</v>
+        <v>88.25</v>
       </c>
       <c r="D1351">
-        <v>0.8</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="1352" spans="1:4" x14ac:dyDescent="0.25">
@@ -19924,10 +19915,10 @@
         <v>9</v>
       </c>
       <c r="C1352">
-        <v>107.51</v>
+        <v>116.84</v>
       </c>
       <c r="D1352">
-        <v>28.96</v>
+        <v>28.59</v>
       </c>
     </row>
     <row r="1353" spans="1:4" x14ac:dyDescent="0.25">
@@ -19938,7 +19929,7 @@
         <v>10</v>
       </c>
       <c r="C1353">
-        <v>107.51</v>
+        <v>116.84</v>
       </c>
       <c r="D1353">
         <v>0</v>
@@ -19952,10 +19943,10 @@
         <v>11</v>
       </c>
       <c r="C1354">
-        <v>110.81</v>
+        <v>120.03</v>
       </c>
       <c r="D1354">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="1355" spans="1:4" x14ac:dyDescent="0.25">
@@ -19966,10 +19957,10 @@
         <v>12</v>
       </c>
       <c r="C1355">
-        <v>150.11000000000001</v>
+        <v>120.03</v>
       </c>
       <c r="D1355">
-        <v>39.299999999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1356" spans="1:4" x14ac:dyDescent="0.25">
@@ -19980,10 +19971,10 @@
         <v>13</v>
       </c>
       <c r="C1356">
-        <v>150.11000000000001</v>
+        <v>120.13</v>
       </c>
       <c r="D1356">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="1357" spans="1:4" x14ac:dyDescent="0.25">
@@ -19994,10 +19985,10 @@
         <v>14</v>
       </c>
       <c r="C1357">
-        <v>150.11000000000001</v>
+        <v>161.34</v>
       </c>
       <c r="D1357">
-        <v>0</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="1358" spans="1:4" x14ac:dyDescent="0.25">
@@ -20008,10 +19999,10 @@
         <v>5</v>
       </c>
       <c r="C1358">
-        <v>30.77</v>
+        <v>10.9</v>
       </c>
       <c r="D1358">
-        <v>30.77</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="1359" spans="1:4" x14ac:dyDescent="0.25">
@@ -20022,10 +20013,10 @@
         <v>6</v>
       </c>
       <c r="C1359">
-        <v>41</v>
+        <v>10.9</v>
       </c>
       <c r="D1359">
-        <v>10.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1360" spans="1:4" x14ac:dyDescent="0.25">
@@ -20036,10 +20027,10 @@
         <v>7</v>
       </c>
       <c r="C1360">
-        <v>81.8</v>
+        <v>15.53</v>
       </c>
       <c r="D1360">
-        <v>40.799999999999997</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="1361" spans="1:4" x14ac:dyDescent="0.25">
@@ -20050,10 +20041,10 @@
         <v>8</v>
       </c>
       <c r="C1361">
-        <v>88.25</v>
+        <v>38.26</v>
       </c>
       <c r="D1361">
-        <v>6.45</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="1362" spans="1:4" x14ac:dyDescent="0.25">
@@ -20064,10 +20055,10 @@
         <v>9</v>
       </c>
       <c r="C1362">
-        <v>116.84</v>
+        <v>121.02</v>
       </c>
       <c r="D1362">
-        <v>28.59</v>
+        <v>82.76</v>
       </c>
     </row>
     <row r="1363" spans="1:4" x14ac:dyDescent="0.25">
@@ -20078,10 +20069,10 @@
         <v>10</v>
       </c>
       <c r="C1363">
-        <v>116.84</v>
+        <v>121.91</v>
       </c>
       <c r="D1363">
-        <v>0</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="1364" spans="1:4" x14ac:dyDescent="0.25">
@@ -20092,10 +20083,10 @@
         <v>11</v>
       </c>
       <c r="C1364">
-        <v>120.03</v>
+        <v>125.23</v>
       </c>
       <c r="D1364">
-        <v>3.19</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="1365" spans="1:4" x14ac:dyDescent="0.25">
@@ -20106,7 +20097,7 @@
         <v>12</v>
       </c>
       <c r="C1365">
-        <v>120.03</v>
+        <v>125.23</v>
       </c>
       <c r="D1365">
         <v>0</v>
@@ -20120,10 +20111,10 @@
         <v>13</v>
       </c>
       <c r="C1366">
-        <v>120.13</v>
+        <v>136.85</v>
       </c>
       <c r="D1366">
-        <v>0.1</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="1367" spans="1:4" x14ac:dyDescent="0.25">
@@ -20134,10 +20125,10 @@
         <v>14</v>
       </c>
       <c r="C1367">
-        <v>161.34</v>
+        <v>142.6</v>
       </c>
       <c r="D1367">
-        <v>41.21</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="1368" spans="1:4" x14ac:dyDescent="0.25">
@@ -20148,10 +20139,10 @@
         <v>5</v>
       </c>
       <c r="C1368">
-        <v>10.9</v>
+        <v>2</v>
       </c>
       <c r="D1368">
-        <v>10.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1369" spans="1:4" x14ac:dyDescent="0.25">
@@ -20162,10 +20153,10 @@
         <v>6</v>
       </c>
       <c r="C1369">
-        <v>10.9</v>
+        <v>14.6</v>
       </c>
       <c r="D1369">
-        <v>0</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="1370" spans="1:4" x14ac:dyDescent="0.25">
@@ -20176,10 +20167,10 @@
         <v>7</v>
       </c>
       <c r="C1370">
-        <v>15.53</v>
+        <v>28.76</v>
       </c>
       <c r="D1370">
-        <v>4.63</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="1371" spans="1:4" x14ac:dyDescent="0.25">
@@ -20190,10 +20181,10 @@
         <v>8</v>
       </c>
       <c r="C1371">
-        <v>38.26</v>
+        <v>116.74</v>
       </c>
       <c r="D1371">
-        <v>22.73</v>
+        <v>87.98</v>
       </c>
     </row>
     <row r="1372" spans="1:4" x14ac:dyDescent="0.25">
@@ -20204,10 +20195,10 @@
         <v>9</v>
       </c>
       <c r="C1372">
-        <v>121.02</v>
+        <v>140.6</v>
       </c>
       <c r="D1372">
-        <v>82.76</v>
+        <v>23.86</v>
       </c>
     </row>
     <row r="1373" spans="1:4" x14ac:dyDescent="0.25">
@@ -20218,10 +20209,10 @@
         <v>10</v>
       </c>
       <c r="C1373">
-        <v>121.91</v>
+        <v>140.6</v>
       </c>
       <c r="D1373">
-        <v>0.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1374" spans="1:4" x14ac:dyDescent="0.25">
@@ -20232,10 +20223,10 @@
         <v>11</v>
       </c>
       <c r="C1374">
-        <v>125.23</v>
+        <v>143.71</v>
       </c>
       <c r="D1374">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="1375" spans="1:4" x14ac:dyDescent="0.25">
@@ -20246,10 +20237,10 @@
         <v>12</v>
       </c>
       <c r="C1375">
-        <v>125.23</v>
+        <v>185.53</v>
       </c>
       <c r="D1375">
-        <v>0</v>
+        <v>41.82</v>
       </c>
     </row>
     <row r="1376" spans="1:4" x14ac:dyDescent="0.25">
@@ -20260,10 +20251,10 @@
         <v>13</v>
       </c>
       <c r="C1376">
-        <v>136.85</v>
+        <v>185.53</v>
       </c>
       <c r="D1376">
-        <v>11.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1377" spans="1:4" x14ac:dyDescent="0.25">
@@ -20274,10 +20265,10 @@
         <v>14</v>
       </c>
       <c r="C1377">
-        <v>142.6</v>
+        <v>185.53</v>
       </c>
       <c r="D1377">
-        <v>5.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1378" spans="1:4" x14ac:dyDescent="0.25">
@@ -20288,10 +20279,10 @@
         <v>5</v>
       </c>
       <c r="C1378">
-        <v>2</v>
+        <v>12.13</v>
       </c>
       <c r="D1378">
-        <v>2</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="1379" spans="1:4" x14ac:dyDescent="0.25">
@@ -20302,10 +20293,10 @@
         <v>6</v>
       </c>
       <c r="C1379">
-        <v>14.6</v>
+        <v>34.950000000000003</v>
       </c>
       <c r="D1379">
-        <v>12.6</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="1380" spans="1:4" x14ac:dyDescent="0.25">
@@ -20316,10 +20307,10 @@
         <v>7</v>
       </c>
       <c r="C1380">
-        <v>28.76</v>
+        <v>121.85</v>
       </c>
       <c r="D1380">
-        <v>14.16</v>
+        <v>86.9</v>
       </c>
     </row>
     <row r="1381" spans="1:4" x14ac:dyDescent="0.25">
@@ -20330,10 +20321,10 @@
         <v>8</v>
       </c>
       <c r="C1381">
-        <v>116.74</v>
+        <v>135.72</v>
       </c>
       <c r="D1381">
-        <v>87.98</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="1382" spans="1:4" x14ac:dyDescent="0.25">
@@ -20344,10 +20335,10 @@
         <v>9</v>
       </c>
       <c r="C1382">
-        <v>140.6</v>
+        <v>153.46</v>
       </c>
       <c r="D1382">
-        <v>23.86</v>
+        <v>17.739999999999998</v>
       </c>
     </row>
     <row r="1383" spans="1:4" x14ac:dyDescent="0.25">
@@ -20358,10 +20349,10 @@
         <v>10</v>
       </c>
       <c r="C1383">
-        <v>140.6</v>
+        <v>153.69999999999999</v>
       </c>
       <c r="D1383">
-        <v>0</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="1384" spans="1:4" x14ac:dyDescent="0.25">
@@ -20372,10 +20363,10 @@
         <v>11</v>
       </c>
       <c r="C1384">
-        <v>143.71</v>
+        <v>156.78</v>
       </c>
       <c r="D1384">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="1385" spans="1:4" x14ac:dyDescent="0.25">
@@ -20386,10 +20377,10 @@
         <v>12</v>
       </c>
       <c r="C1385">
-        <v>185.53</v>
+        <v>172.39</v>
       </c>
       <c r="D1385">
-        <v>41.82</v>
+        <v>15.61</v>
       </c>
     </row>
     <row r="1386" spans="1:4" x14ac:dyDescent="0.25">
@@ -20400,10 +20391,10 @@
         <v>13</v>
       </c>
       <c r="C1386">
-        <v>185.53</v>
+        <v>186.38</v>
       </c>
       <c r="D1386">
-        <v>0</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="1387" spans="1:4" x14ac:dyDescent="0.25">
@@ -20414,10 +20405,10 @@
         <v>14</v>
       </c>
       <c r="C1387">
-        <v>185.53</v>
+        <v>195.53</v>
       </c>
       <c r="D1387">
-        <v>0</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="1388" spans="1:4" x14ac:dyDescent="0.25">
@@ -20428,10 +20419,10 @@
         <v>5</v>
       </c>
       <c r="C1388">
-        <v>12.13</v>
+        <v>6.5</v>
       </c>
       <c r="D1388">
-        <v>12.13</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="1389" spans="1:4" x14ac:dyDescent="0.25">
@@ -20442,10 +20433,10 @@
         <v>6</v>
       </c>
       <c r="C1389">
-        <v>34.950000000000003</v>
+        <v>55.11</v>
       </c>
       <c r="D1389">
-        <v>22.82</v>
+        <v>48.61</v>
       </c>
     </row>
     <row r="1390" spans="1:4" x14ac:dyDescent="0.25">
@@ -20456,10 +20447,10 @@
         <v>7</v>
       </c>
       <c r="C1390">
-        <v>121.85</v>
+        <v>124.94</v>
       </c>
       <c r="D1390">
-        <v>86.9</v>
+        <v>69.83</v>
       </c>
     </row>
     <row r="1391" spans="1:4" x14ac:dyDescent="0.25">
@@ -20470,10 +20461,10 @@
         <v>8</v>
       </c>
       <c r="C1391">
-        <v>135.72</v>
+        <v>131.94</v>
       </c>
       <c r="D1391">
-        <v>13.87</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1392" spans="1:4" x14ac:dyDescent="0.25">
@@ -20484,10 +20475,10 @@
         <v>9</v>
       </c>
       <c r="C1392">
-        <v>153.46</v>
+        <v>157.77000000000001</v>
       </c>
       <c r="D1392">
-        <v>17.739999999999998</v>
+        <v>25.83</v>
       </c>
     </row>
     <row r="1393" spans="1:4" x14ac:dyDescent="0.25">
@@ -20498,10 +20489,10 @@
         <v>10</v>
       </c>
       <c r="C1393">
-        <v>153.69999999999999</v>
+        <v>157.77000000000001</v>
       </c>
       <c r="D1393">
-        <v>0.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1394" spans="1:4" x14ac:dyDescent="0.25">
@@ -20512,10 +20503,10 @@
         <v>11</v>
       </c>
       <c r="C1394">
-        <v>156.78</v>
+        <v>160.66999999999999</v>
       </c>
       <c r="D1394">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="1395" spans="1:4" x14ac:dyDescent="0.25">
@@ -20526,10 +20517,10 @@
         <v>12</v>
       </c>
       <c r="C1395">
-        <v>172.39</v>
+        <v>201.87</v>
       </c>
       <c r="D1395">
-        <v>15.61</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="1396" spans="1:4" x14ac:dyDescent="0.25">
@@ -20540,10 +20531,10 @@
         <v>13</v>
       </c>
       <c r="C1396">
-        <v>186.38</v>
+        <v>201.87</v>
       </c>
       <c r="D1396">
-        <v>13.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1397" spans="1:4" x14ac:dyDescent="0.25">
@@ -20554,10 +20545,10 @@
         <v>14</v>
       </c>
       <c r="C1397">
-        <v>195.53</v>
+        <v>201.87</v>
       </c>
       <c r="D1397">
-        <v>9.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1398" spans="1:4" x14ac:dyDescent="0.25">
@@ -20568,10 +20559,10 @@
         <v>5</v>
       </c>
       <c r="C1398">
-        <v>6.5</v>
+        <v>14.13</v>
       </c>
       <c r="D1398">
-        <v>6.5</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="1399" spans="1:4" x14ac:dyDescent="0.25">
@@ -20582,10 +20573,10 @@
         <v>6</v>
       </c>
       <c r="C1399">
-        <v>55.11</v>
+        <v>61.5</v>
       </c>
       <c r="D1399">
-        <v>48.61</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="1400" spans="1:4" x14ac:dyDescent="0.25">
@@ -20596,10 +20587,10 @@
         <v>7</v>
       </c>
       <c r="C1400">
-        <v>124.94</v>
+        <v>70.72</v>
       </c>
       <c r="D1400">
-        <v>69.83</v>
+        <v>9.2200000000000006</v>
       </c>
     </row>
     <row r="1401" spans="1:4" x14ac:dyDescent="0.25">
@@ -20610,10 +20601,10 @@
         <v>8</v>
       </c>
       <c r="C1401">
-        <v>131.94</v>
+        <v>79.430000000000007</v>
       </c>
       <c r="D1401">
-        <v>7</v>
+        <v>8.7100000000000009</v>
       </c>
     </row>
     <row r="1402" spans="1:4" x14ac:dyDescent="0.25">
@@ -20624,10 +20615,10 @@
         <v>9</v>
       </c>
       <c r="C1402">
-        <v>157.77000000000001</v>
+        <v>112.5</v>
       </c>
       <c r="D1402">
-        <v>25.83</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="1403" spans="1:4" x14ac:dyDescent="0.25">
@@ -20638,7 +20629,7 @@
         <v>10</v>
       </c>
       <c r="C1403">
-        <v>157.77000000000001</v>
+        <v>112.5</v>
       </c>
       <c r="D1403">
         <v>0</v>
@@ -20652,10 +20643,10 @@
         <v>11</v>
       </c>
       <c r="C1404">
-        <v>160.66999999999999</v>
+        <v>115.84</v>
       </c>
       <c r="D1404">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="1405" spans="1:4" x14ac:dyDescent="0.25">
@@ -20666,10 +20657,10 @@
         <v>12</v>
       </c>
       <c r="C1405">
-        <v>201.87</v>
+        <v>144.61000000000001</v>
       </c>
       <c r="D1405">
-        <v>41.2</v>
+        <v>28.77</v>
       </c>
     </row>
     <row r="1406" spans="1:4" x14ac:dyDescent="0.25">
@@ -20680,10 +20671,10 @@
         <v>13</v>
       </c>
       <c r="C1406">
-        <v>201.87</v>
+        <v>144.91</v>
       </c>
       <c r="D1406">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="1407" spans="1:4" x14ac:dyDescent="0.25">
@@ -20694,10 +20685,10 @@
         <v>14</v>
       </c>
       <c r="C1407">
-        <v>201.87</v>
+        <v>149.61000000000001</v>
       </c>
       <c r="D1407">
-        <v>0</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="1408" spans="1:4" x14ac:dyDescent="0.25">
@@ -20708,10 +20699,10 @@
         <v>5</v>
       </c>
       <c r="C1408">
-        <v>14.13</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D1408">
-        <v>14.13</v>
+        <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="1409" spans="1:4" x14ac:dyDescent="0.25">
@@ -20722,10 +20713,10 @@
         <v>6</v>
       </c>
       <c r="C1409">
-        <v>61.5</v>
+        <v>21.35</v>
       </c>
       <c r="D1409">
-        <v>47.37</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="1410" spans="1:4" x14ac:dyDescent="0.25">
@@ -20736,10 +20727,10 @@
         <v>7</v>
       </c>
       <c r="C1410">
-        <v>70.72</v>
+        <v>68.42</v>
       </c>
       <c r="D1410">
-        <v>9.2200000000000006</v>
+        <v>47.07</v>
       </c>
     </row>
     <row r="1411" spans="1:4" x14ac:dyDescent="0.25">
@@ -20750,10 +20741,10 @@
         <v>8</v>
       </c>
       <c r="C1411">
-        <v>79.430000000000007</v>
+        <v>89.9</v>
       </c>
       <c r="D1411">
-        <v>8.7100000000000009</v>
+        <v>21.48</v>
       </c>
     </row>
     <row r="1412" spans="1:4" x14ac:dyDescent="0.25">
@@ -20764,10 +20755,10 @@
         <v>9</v>
       </c>
       <c r="C1412">
-        <v>112.5</v>
+        <v>103.02</v>
       </c>
       <c r="D1412">
-        <v>33.07</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="1413" spans="1:4" x14ac:dyDescent="0.25">
@@ -20778,7 +20769,7 @@
         <v>10</v>
       </c>
       <c r="C1413">
-        <v>112.5</v>
+        <v>103.02</v>
       </c>
       <c r="D1413">
         <v>0</v>
@@ -20792,10 +20783,10 @@
         <v>11</v>
       </c>
       <c r="C1414">
-        <v>115.84</v>
+        <v>106.26</v>
       </c>
       <c r="D1414">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="1415" spans="1:4" x14ac:dyDescent="0.25">
@@ -20806,10 +20797,10 @@
         <v>12</v>
       </c>
       <c r="C1415">
-        <v>144.61000000000001</v>
+        <v>107.56</v>
       </c>
       <c r="D1415">
-        <v>28.77</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="1416" spans="1:4" x14ac:dyDescent="0.25">
@@ -20820,10 +20811,10 @@
         <v>13</v>
       </c>
       <c r="C1416">
-        <v>144.91</v>
+        <v>126.6</v>
       </c>
       <c r="D1416">
-        <v>0.3</v>
+        <v>19.04</v>
       </c>
     </row>
     <row r="1417" spans="1:4" x14ac:dyDescent="0.25">
@@ -20834,10 +20825,10 @@
         <v>14</v>
       </c>
       <c r="C1417">
-        <v>149.61000000000001</v>
+        <v>143.35</v>
       </c>
       <c r="D1417">
-        <v>4.7</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="1418" spans="1:4" x14ac:dyDescent="0.25">
@@ -20848,10 +20839,10 @@
         <v>5</v>
       </c>
       <c r="C1418">
-        <v>4.5999999999999996</v>
+        <v>21.7</v>
       </c>
       <c r="D1418">
-        <v>4.5999999999999996</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="1419" spans="1:4" x14ac:dyDescent="0.25">
@@ -20862,10 +20853,10 @@
         <v>6</v>
       </c>
       <c r="C1419">
-        <v>21.35</v>
+        <v>28.9</v>
       </c>
       <c r="D1419">
-        <v>16.75</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="1420" spans="1:4" x14ac:dyDescent="0.25">
@@ -20876,10 +20867,10 @@
         <v>7</v>
       </c>
       <c r="C1420">
-        <v>68.42</v>
+        <v>51.94</v>
       </c>
       <c r="D1420">
-        <v>47.07</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="1421" spans="1:4" x14ac:dyDescent="0.25">
@@ -20890,10 +20881,10 @@
         <v>8</v>
       </c>
       <c r="C1421">
-        <v>89.9</v>
+        <v>57.4</v>
       </c>
       <c r="D1421">
-        <v>21.48</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="1422" spans="1:4" x14ac:dyDescent="0.25">
@@ -20904,10 +20895,10 @@
         <v>9</v>
       </c>
       <c r="C1422">
-        <v>103.02</v>
+        <v>86.57</v>
       </c>
       <c r="D1422">
-        <v>13.12</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="1423" spans="1:4" x14ac:dyDescent="0.25">
@@ -20918,7 +20909,7 @@
         <v>10</v>
       </c>
       <c r="C1423">
-        <v>103.02</v>
+        <v>86.57</v>
       </c>
       <c r="D1423">
         <v>0</v>
@@ -20932,10 +20923,10 @@
         <v>11</v>
       </c>
       <c r="C1424">
-        <v>106.26</v>
+        <v>89.84</v>
       </c>
       <c r="D1424">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="1425" spans="1:4" x14ac:dyDescent="0.25">
@@ -20946,10 +20937,10 @@
         <v>12</v>
       </c>
       <c r="C1425">
-        <v>107.56</v>
+        <v>106.4</v>
       </c>
       <c r="D1425">
-        <v>1.3</v>
+        <v>16.559999999999999</v>
       </c>
     </row>
     <row r="1426" spans="1:4" x14ac:dyDescent="0.25">
@@ -20960,10 +20951,10 @@
         <v>13</v>
       </c>
       <c r="C1426">
-        <v>126.6</v>
+        <v>109.4</v>
       </c>
       <c r="D1426">
-        <v>19.04</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1427" spans="1:4" x14ac:dyDescent="0.25">
@@ -20974,10 +20965,10 @@
         <v>14</v>
       </c>
       <c r="C1427">
-        <v>143.35</v>
+        <v>128.01</v>
       </c>
       <c r="D1427">
-        <v>16.75</v>
+        <v>18.61</v>
       </c>
     </row>
     <row r="1428" spans="1:4" x14ac:dyDescent="0.25">
@@ -20988,10 +20979,10 @@
         <v>5</v>
       </c>
       <c r="C1428">
-        <v>21.7</v>
+        <v>10.8</v>
       </c>
       <c r="D1428">
-        <v>21.7</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="1429" spans="1:4" x14ac:dyDescent="0.25">
@@ -21002,10 +20993,10 @@
         <v>6</v>
       </c>
       <c r="C1429">
-        <v>28.9</v>
+        <v>41.2</v>
       </c>
       <c r="D1429">
-        <v>7.2</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="1430" spans="1:4" x14ac:dyDescent="0.25">
@@ -21016,10 +21007,10 @@
         <v>7</v>
       </c>
       <c r="C1430">
-        <v>51.94</v>
+        <v>52.3</v>
       </c>
       <c r="D1430">
-        <v>23.04</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="1431" spans="1:4" x14ac:dyDescent="0.25">
@@ -21030,10 +21021,10 @@
         <v>8</v>
       </c>
       <c r="C1431">
-        <v>57.4</v>
+        <v>61.5</v>
       </c>
       <c r="D1431">
-        <v>5.46</v>
+        <v>9.1999999999999993</v>
       </c>
     </row>
     <row r="1432" spans="1:4" x14ac:dyDescent="0.25">
@@ -21044,10 +21035,10 @@
         <v>9</v>
       </c>
       <c r="C1432">
-        <v>86.57</v>
+        <v>61.8</v>
       </c>
       <c r="D1432">
-        <v>29.17</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="1433" spans="1:4" x14ac:dyDescent="0.25">
@@ -21058,7 +21049,7 @@
         <v>10</v>
       </c>
       <c r="C1433">
-        <v>86.57</v>
+        <v>61.8</v>
       </c>
       <c r="D1433">
         <v>0</v>
@@ -21072,10 +21063,10 @@
         <v>11</v>
       </c>
       <c r="C1434">
-        <v>89.84</v>
+        <v>65.400000000000006</v>
       </c>
       <c r="D1434">
-        <v>3.27</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="1435" spans="1:4" x14ac:dyDescent="0.25">
@@ -21086,10 +21077,10 @@
         <v>12</v>
       </c>
       <c r="C1435">
-        <v>106.4</v>
+        <v>65.400000000000006</v>
       </c>
       <c r="D1435">
-        <v>16.559999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1436" spans="1:4" x14ac:dyDescent="0.25">
@@ -21100,10 +21091,10 @@
         <v>13</v>
       </c>
       <c r="C1436">
-        <v>109.4</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="D1436">
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="1437" spans="1:4" x14ac:dyDescent="0.25">
@@ -21114,10 +21105,10 @@
         <v>14</v>
       </c>
       <c r="C1437">
-        <v>128.01</v>
+        <v>104.35</v>
       </c>
       <c r="D1437">
-        <v>18.61</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="1438" spans="1:4" x14ac:dyDescent="0.25">
@@ -21128,10 +21119,10 @@
         <v>5</v>
       </c>
       <c r="C1438">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="D1438">
-        <v>10.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1439" spans="1:4" x14ac:dyDescent="0.25">
@@ -21142,10 +21133,10 @@
         <v>6</v>
       </c>
       <c r="C1439">
-        <v>41.2</v>
+        <v>34.42</v>
       </c>
       <c r="D1439">
-        <v>30.4</v>
+        <v>34.42</v>
       </c>
     </row>
     <row r="1440" spans="1:4" x14ac:dyDescent="0.25">
@@ -21156,10 +21147,10 @@
         <v>7</v>
       </c>
       <c r="C1440">
-        <v>52.3</v>
+        <v>34.42</v>
       </c>
       <c r="D1440">
-        <v>11.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1441" spans="1:4" x14ac:dyDescent="0.25">
@@ -21170,10 +21161,10 @@
         <v>8</v>
       </c>
       <c r="C1441">
-        <v>61.5</v>
+        <v>39.24</v>
       </c>
       <c r="D1441">
-        <v>9.1999999999999993</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="1442" spans="1:4" x14ac:dyDescent="0.25">
@@ -21184,10 +21175,10 @@
         <v>9</v>
       </c>
       <c r="C1442">
-        <v>61.8</v>
+        <v>41.13</v>
       </c>
       <c r="D1442">
-        <v>0.3</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="1443" spans="1:4" x14ac:dyDescent="0.25">
@@ -21198,10 +21189,10 @@
         <v>10</v>
       </c>
       <c r="C1443">
-        <v>61.8</v>
+        <v>41.26</v>
       </c>
       <c r="D1443">
-        <v>0</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="1444" spans="1:4" x14ac:dyDescent="0.25">
@@ -21212,10 +21203,10 @@
         <v>11</v>
       </c>
       <c r="C1444">
-        <v>65.400000000000006</v>
+        <v>44.56</v>
       </c>
       <c r="D1444">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="1445" spans="1:4" x14ac:dyDescent="0.25">
@@ -21226,10 +21217,10 @@
         <v>12</v>
       </c>
       <c r="C1445">
-        <v>65.400000000000006</v>
+        <v>57.7</v>
       </c>
       <c r="D1445">
-        <v>0</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="1446" spans="1:4" x14ac:dyDescent="0.25">
@@ -21240,10 +21231,10 @@
         <v>13</v>
       </c>
       <c r="C1446">
-        <v>67.599999999999994</v>
+        <v>59.6</v>
       </c>
       <c r="D1446">
-        <v>2.2000000000000002</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="1447" spans="1:4" x14ac:dyDescent="0.25">
@@ -21254,10 +21245,10 @@
         <v>14</v>
       </c>
       <c r="C1447">
-        <v>104.35</v>
+        <v>83.39</v>
       </c>
       <c r="D1447">
-        <v>36.75</v>
+        <v>23.79</v>
       </c>
     </row>
     <row r="1448" spans="1:4" x14ac:dyDescent="0.25">
@@ -21268,10 +21259,10 @@
         <v>5</v>
       </c>
       <c r="C1448">
-        <v>0</v>
+        <v>42.46</v>
       </c>
       <c r="D1448">
-        <v>0</v>
+        <v>42.46</v>
       </c>
     </row>
     <row r="1449" spans="1:4" x14ac:dyDescent="0.25">
@@ -21282,10 +21273,10 @@
         <v>6</v>
       </c>
       <c r="C1449">
-        <v>34.42</v>
+        <v>58.08</v>
       </c>
       <c r="D1449">
-        <v>34.42</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="1450" spans="1:4" x14ac:dyDescent="0.25">
@@ -21296,10 +21287,10 @@
         <v>7</v>
       </c>
       <c r="C1450">
-        <v>34.42</v>
+        <v>59.24</v>
       </c>
       <c r="D1450">
-        <v>0</v>
+        <v>1.1599999999999999</v>
       </c>
     </row>
     <row r="1451" spans="1:4" x14ac:dyDescent="0.25">
@@ -21310,10 +21301,10 @@
         <v>8</v>
       </c>
       <c r="C1451">
-        <v>39.24</v>
+        <v>89.17</v>
       </c>
       <c r="D1451">
-        <v>4.82</v>
+        <v>29.93</v>
       </c>
     </row>
     <row r="1452" spans="1:4" x14ac:dyDescent="0.25">
@@ -21324,10 +21315,10 @@
         <v>9</v>
       </c>
       <c r="C1452">
-        <v>41.13</v>
+        <v>96.66</v>
       </c>
       <c r="D1452">
-        <v>1.89</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="1453" spans="1:4" x14ac:dyDescent="0.25">
@@ -21338,10 +21329,10 @@
         <v>10</v>
       </c>
       <c r="C1453">
-        <v>41.26</v>
+        <v>96.66</v>
       </c>
       <c r="D1453">
-        <v>0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1454" spans="1:4" x14ac:dyDescent="0.25">
@@ -21352,10 +21343,10 @@
         <v>11</v>
       </c>
       <c r="C1454">
-        <v>44.56</v>
+        <v>100.05</v>
       </c>
       <c r="D1454">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="1455" spans="1:4" x14ac:dyDescent="0.25">
@@ -21366,10 +21357,10 @@
         <v>12</v>
       </c>
       <c r="C1455">
-        <v>57.7</v>
+        <v>138.30000000000001</v>
       </c>
       <c r="D1455">
-        <v>13.14</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="1456" spans="1:4" x14ac:dyDescent="0.25">
@@ -21380,10 +21371,10 @@
         <v>13</v>
       </c>
       <c r="C1456">
-        <v>59.6</v>
+        <v>138.30000000000001</v>
       </c>
       <c r="D1456">
-        <v>1.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1457" spans="1:4" x14ac:dyDescent="0.25">
@@ -21394,10 +21385,10 @@
         <v>14</v>
       </c>
       <c r="C1457">
-        <v>83.39</v>
+        <v>138.30000000000001</v>
       </c>
       <c r="D1457">
-        <v>23.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1458" spans="1:4" x14ac:dyDescent="0.25">
@@ -21408,10 +21399,10 @@
         <v>5</v>
       </c>
       <c r="C1458">
-        <v>42.46</v>
+        <v>21.53</v>
       </c>
       <c r="D1458">
-        <v>42.46</v>
+        <v>21.53</v>
       </c>
     </row>
     <row r="1459" spans="1:4" x14ac:dyDescent="0.25">
@@ -21422,10 +21413,10 @@
         <v>6</v>
       </c>
       <c r="C1459">
-        <v>58.08</v>
+        <v>40.81</v>
       </c>
       <c r="D1459">
-        <v>15.62</v>
+        <v>19.28</v>
       </c>
     </row>
     <row r="1460" spans="1:4" x14ac:dyDescent="0.25">
@@ -21436,10 +21427,10 @@
         <v>7</v>
       </c>
       <c r="C1460">
-        <v>59.24</v>
+        <v>67.44</v>
       </c>
       <c r="D1460">
-        <v>1.1599999999999999</v>
+        <v>26.63</v>
       </c>
     </row>
     <row r="1461" spans="1:4" x14ac:dyDescent="0.25">
@@ -21450,10 +21441,10 @@
         <v>8</v>
       </c>
       <c r="C1461">
-        <v>89.17</v>
+        <v>67.84</v>
       </c>
       <c r="D1461">
-        <v>29.93</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="1462" spans="1:4" x14ac:dyDescent="0.25">
@@ -21464,10 +21455,10 @@
         <v>9</v>
       </c>
       <c r="C1462">
-        <v>96.66</v>
+        <v>104.84</v>
       </c>
       <c r="D1462">
-        <v>7.49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1463" spans="1:4" x14ac:dyDescent="0.25">
@@ -21478,7 +21469,7 @@
         <v>10</v>
       </c>
       <c r="C1463">
-        <v>96.66</v>
+        <v>104.84</v>
       </c>
       <c r="D1463">
         <v>0</v>
@@ -21492,10 +21483,10 @@
         <v>11</v>
       </c>
       <c r="C1464">
-        <v>100.05</v>
+        <v>108.06</v>
       </c>
       <c r="D1464">
-        <v>3.39</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="1465" spans="1:4" x14ac:dyDescent="0.25">
@@ -21506,10 +21497,10 @@
         <v>12</v>
       </c>
       <c r="C1465">
-        <v>138.30000000000001</v>
+        <v>149.80000000000001</v>
       </c>
       <c r="D1465">
-        <v>38.25</v>
+        <v>41.74</v>
       </c>
     </row>
     <row r="1466" spans="1:4" x14ac:dyDescent="0.25">
@@ -21520,7 +21511,7 @@
         <v>13</v>
       </c>
       <c r="C1466">
-        <v>138.30000000000001</v>
+        <v>149.80000000000001</v>
       </c>
       <c r="D1466">
         <v>0</v>
@@ -21534,7 +21525,7 @@
         <v>14</v>
       </c>
       <c r="C1467">
-        <v>138.30000000000001</v>
+        <v>149.80000000000001</v>
       </c>
       <c r="D1467">
         <v>0</v>
@@ -21548,10 +21539,10 @@
         <v>5</v>
       </c>
       <c r="C1468">
-        <v>40.28</v>
+        <v>5.8</v>
       </c>
       <c r="D1468">
-        <v>40.28</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="1469" spans="1:4" x14ac:dyDescent="0.25">
@@ -21562,10 +21553,10 @@
         <v>6</v>
       </c>
       <c r="C1469">
-        <v>76.650000000000006</v>
+        <v>29.4</v>
       </c>
       <c r="D1469">
-        <v>36.369999999999997</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="1470" spans="1:4" x14ac:dyDescent="0.25">
@@ -21576,10 +21567,10 @@
         <v>7</v>
       </c>
       <c r="C1470">
-        <v>78.55</v>
+        <v>70.48</v>
       </c>
       <c r="D1470">
-        <v>1.9</v>
+        <v>41.08</v>
       </c>
     </row>
     <row r="1471" spans="1:4" x14ac:dyDescent="0.25">
@@ -21590,10 +21581,10 @@
         <v>8</v>
       </c>
       <c r="C1471">
-        <v>81.08</v>
+        <v>70.58</v>
       </c>
       <c r="D1471">
-        <v>2.5299999999999998</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="1472" spans="1:4" x14ac:dyDescent="0.25">
@@ -21604,10 +21595,10 @@
         <v>9</v>
       </c>
       <c r="C1472">
-        <v>95.82</v>
+        <v>119.55</v>
       </c>
       <c r="D1472">
-        <v>14.74</v>
+        <v>48.97</v>
       </c>
     </row>
     <row r="1473" spans="1:4" x14ac:dyDescent="0.25">
@@ -21618,7 +21609,7 @@
         <v>10</v>
       </c>
       <c r="C1473">
-        <v>95.82</v>
+        <v>119.55</v>
       </c>
       <c r="D1473">
         <v>0</v>
@@ -21632,52 +21623,52 @@
         <v>11</v>
       </c>
       <c r="C1474">
-        <v>98.82</v>
+        <v>123.26</v>
       </c>
       <c r="D1474">
-        <v>3</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="1475" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1475" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B1475" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C1475">
-        <v>31.66</v>
+        <v>123.26</v>
       </c>
       <c r="D1475">
-        <v>31.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1476" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B1476" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C1476">
-        <v>50.32</v>
+        <v>124.46</v>
       </c>
       <c r="D1476">
-        <v>18.66</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="1477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1477" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B1477" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C1477">
-        <v>67.16</v>
+        <v>160.69</v>
       </c>
       <c r="D1477">
-        <v>16.84</v>
+        <v>36.229999999999997</v>
       </c>
     </row>
     <row r="1478" spans="1:4" x14ac:dyDescent="0.25">
@@ -21685,13 +21676,13 @@
         <v>170</v>
       </c>
       <c r="B1478" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C1478">
-        <v>67.86</v>
+        <v>49.75</v>
       </c>
       <c r="D1478">
-        <v>0.7</v>
+        <v>49.75</v>
       </c>
     </row>
     <row r="1479" spans="1:4" x14ac:dyDescent="0.25">
@@ -21699,13 +21690,13 @@
         <v>170</v>
       </c>
       <c r="B1479" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C1479">
-        <v>96.46</v>
+        <v>49.75</v>
       </c>
       <c r="D1479">
-        <v>28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1480" spans="1:4" x14ac:dyDescent="0.25">
@@ -21713,13 +21704,13 @@
         <v>170</v>
       </c>
       <c r="B1480" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C1480">
-        <v>97.83</v>
+        <v>52.93</v>
       </c>
       <c r="D1480">
-        <v>1.37</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="1481" spans="1:4" x14ac:dyDescent="0.25">
@@ -21727,94 +21718,94 @@
         <v>170</v>
       </c>
       <c r="B1481" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C1481">
-        <v>100.83</v>
+        <v>62.19</v>
       </c>
       <c r="D1481">
-        <v>3</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="1482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1482" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B1482" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C1482">
-        <v>21.53</v>
+        <v>71.209999999999994</v>
       </c>
       <c r="D1482">
-        <v>21.53</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="1483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1483" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B1483" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C1483">
-        <v>40.81</v>
+        <v>71.61</v>
       </c>
       <c r="D1483">
-        <v>19.28</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="1484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1484" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B1484" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C1484">
-        <v>67.44</v>
+        <v>74.790000000000006</v>
       </c>
       <c r="D1484">
-        <v>26.63</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="1485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1485" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B1485" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1485">
-        <v>67.84</v>
+        <v>77.040000000000006</v>
       </c>
       <c r="D1485">
-        <v>0.4</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="1486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1486" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B1486" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1486">
-        <v>104.84</v>
+        <v>110.6</v>
       </c>
       <c r="D1486">
-        <v>37</v>
+        <v>33.56</v>
       </c>
     </row>
     <row r="1487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1487" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B1487" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1487">
-        <v>104.84</v>
+        <v>110.6</v>
       </c>
       <c r="D1487">
         <v>0</v>
@@ -21825,13 +21816,13 @@
         <v>171</v>
       </c>
       <c r="B1488" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C1488">
-        <v>108.06</v>
+        <v>12.75</v>
       </c>
       <c r="D1488">
-        <v>3.22</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="1489" spans="1:4" x14ac:dyDescent="0.25">
@@ -21839,13 +21830,13 @@
         <v>171</v>
       </c>
       <c r="B1489" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C1489">
-        <v>149.80000000000001</v>
+        <v>28.45</v>
       </c>
       <c r="D1489">
-        <v>41.74</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="1490" spans="1:4" x14ac:dyDescent="0.25">
@@ -21853,13 +21844,13 @@
         <v>171</v>
       </c>
       <c r="B1490" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1490">
-        <v>149.80000000000001</v>
+        <v>59.16</v>
       </c>
       <c r="D1490">
-        <v>0</v>
+        <v>30.71</v>
       </c>
     </row>
     <row r="1491" spans="1:4" x14ac:dyDescent="0.25">
@@ -21867,94 +21858,94 @@
         <v>171</v>
       </c>
       <c r="B1491" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1491">
-        <v>149.80000000000001</v>
+        <v>61.96</v>
       </c>
       <c r="D1491">
-        <v>0</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="1492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B1492" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C1492">
-        <v>5.8</v>
+        <v>91.85</v>
       </c>
       <c r="D1492">
-        <v>5.8</v>
+        <v>29.89</v>
       </c>
     </row>
     <row r="1493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B1493" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C1493">
-        <v>29.4</v>
+        <v>92</v>
       </c>
       <c r="D1493">
-        <v>23.6</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="1494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B1494" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C1494">
-        <v>70.48</v>
+        <v>95.8</v>
       </c>
       <c r="D1494">
-        <v>41.08</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="1495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B1495" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1495">
-        <v>70.58</v>
+        <v>130.15</v>
       </c>
       <c r="D1495">
-        <v>0.1</v>
+        <v>34.35</v>
       </c>
     </row>
     <row r="1496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B1496" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1496">
-        <v>119.55</v>
+        <v>130.35</v>
       </c>
       <c r="D1496">
-        <v>48.97</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="1497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B1497" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1497">
-        <v>119.55</v>
+        <v>130.35</v>
       </c>
       <c r="D1497">
         <v>0</v>
@@ -21965,13 +21956,13 @@
         <v>172</v>
       </c>
       <c r="B1498" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C1498">
-        <v>123.26</v>
+        <v>6.18</v>
       </c>
       <c r="D1498">
-        <v>3.71</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="1499" spans="1:4" x14ac:dyDescent="0.25">
@@ -21979,13 +21970,13 @@
         <v>172</v>
       </c>
       <c r="B1499" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C1499">
-        <v>123.26</v>
+        <v>37.4</v>
       </c>
       <c r="D1499">
-        <v>0</v>
+        <v>31.22</v>
       </c>
     </row>
     <row r="1500" spans="1:4" x14ac:dyDescent="0.25">
@@ -21993,13 +21984,13 @@
         <v>172</v>
       </c>
       <c r="B1500" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1500">
-        <v>124.46</v>
+        <v>67.89</v>
       </c>
       <c r="D1500">
-        <v>1.2</v>
+        <v>30.49</v>
       </c>
     </row>
     <row r="1501" spans="1:4" x14ac:dyDescent="0.25">
@@ -22007,97 +21998,97 @@
         <v>172</v>
       </c>
       <c r="B1501" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1501">
-        <v>160.69</v>
+        <v>100.17</v>
       </c>
       <c r="D1501">
-        <v>36.229999999999997</v>
+        <v>32.28</v>
       </c>
     </row>
     <row r="1502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B1502" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C1502">
-        <v>49.75</v>
+        <v>101.82</v>
       </c>
       <c r="D1502">
-        <v>49.75</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="1503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B1503" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C1503">
-        <v>49.75</v>
+        <v>101.92</v>
       </c>
       <c r="D1503">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="1504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1504" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B1504" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C1504">
-        <v>52.93</v>
+        <v>105.39</v>
       </c>
       <c r="D1504">
-        <v>3.18</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="1505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1505" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B1505" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1505">
-        <v>62.19</v>
+        <v>105.39</v>
       </c>
       <c r="D1505">
-        <v>9.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1506" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B1506" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1506">
-        <v>71.209999999999994</v>
+        <v>112.72</v>
       </c>
       <c r="D1506">
-        <v>9.02</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="1507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1507" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B1507" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1507">
-        <v>71.61</v>
+        <v>141.77000000000001</v>
       </c>
       <c r="D1507">
-        <v>0.4</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="1508" spans="1:4" x14ac:dyDescent="0.25">
@@ -22105,13 +22096,13 @@
         <v>173</v>
       </c>
       <c r="B1508" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C1508">
-        <v>74.790000000000006</v>
+        <v>2.4</v>
       </c>
       <c r="D1508">
-        <v>3.18</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="1509" spans="1:4" x14ac:dyDescent="0.25">
@@ -22119,13 +22110,13 @@
         <v>173</v>
       </c>
       <c r="B1509" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C1509">
-        <v>77.040000000000006</v>
+        <v>32.5</v>
       </c>
       <c r="D1509">
-        <v>2.25</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="1510" spans="1:4" x14ac:dyDescent="0.25">
@@ -22133,13 +22124,13 @@
         <v>173</v>
       </c>
       <c r="B1510" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1510">
-        <v>110.6</v>
+        <v>86.2</v>
       </c>
       <c r="D1510">
-        <v>33.56</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="1511" spans="1:4" x14ac:dyDescent="0.25">
@@ -22147,97 +22138,97 @@
         <v>173</v>
       </c>
       <c r="B1511" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1511">
-        <v>110.6</v>
+        <v>86.9</v>
       </c>
       <c r="D1511">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="1512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1512" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B1512" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C1512">
-        <v>12.75</v>
+        <v>115.46</v>
       </c>
       <c r="D1512">
-        <v>12.75</v>
+        <v>28.56</v>
       </c>
     </row>
     <row r="1513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1513" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B1513" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C1513">
-        <v>28.45</v>
+        <v>115.46</v>
       </c>
       <c r="D1513">
-        <v>15.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1514" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1514" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B1514" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C1514">
-        <v>59.16</v>
+        <v>118.87</v>
       </c>
       <c r="D1514">
-        <v>30.71</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="1515" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1515" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B1515" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1515">
-        <v>61.96</v>
+        <v>158.76</v>
       </c>
       <c r="D1515">
-        <v>2.8</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="1516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1516" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B1516" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1516">
-        <v>91.85</v>
+        <v>159.63999999999999</v>
       </c>
       <c r="D1516">
-        <v>29.89</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="1517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1517" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B1517" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1517">
-        <v>92</v>
+        <v>159.63999999999999</v>
       </c>
       <c r="D1517">
-        <v>0.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1518" spans="1:4" x14ac:dyDescent="0.25">
@@ -22245,13 +22236,13 @@
         <v>174</v>
       </c>
       <c r="B1518" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C1518">
-        <v>95.8</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="D1518">
-        <v>3.8</v>
+        <v>76.099999999999994</v>
       </c>
     </row>
     <row r="1519" spans="1:4" x14ac:dyDescent="0.25">
@@ -22259,13 +22250,13 @@
         <v>174</v>
       </c>
       <c r="B1519" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C1519">
-        <v>130.15</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="D1519">
-        <v>34.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1520" spans="1:4" x14ac:dyDescent="0.25">
@@ -22273,13 +22264,13 @@
         <v>174</v>
       </c>
       <c r="B1520" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1520">
-        <v>130.35</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="D1520">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1521" spans="1:4" x14ac:dyDescent="0.25">
@@ -22287,10 +22278,10 @@
         <v>174</v>
       </c>
       <c r="B1521" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1521">
-        <v>130.35</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="D1521">
         <v>0</v>
@@ -22298,86 +22289,86 @@
     </row>
     <row r="1522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1522" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B1522" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C1522">
-        <v>6.18</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="D1522">
-        <v>6.18</v>
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="1523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1523" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B1523" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C1523">
-        <v>37.4</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="D1523">
-        <v>31.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1524" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B1524" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C1524">
-        <v>67.89</v>
+        <v>81.400000000000006</v>
       </c>
       <c r="D1524">
-        <v>30.49</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1525" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B1525" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1525">
-        <v>100.17</v>
+        <v>97.68</v>
       </c>
       <c r="D1525">
-        <v>32.28</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="1526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1526" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B1526" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1526">
-        <v>101.82</v>
+        <v>115.91</v>
       </c>
       <c r="D1526">
-        <v>1.65</v>
+        <v>18.23</v>
       </c>
     </row>
     <row r="1527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1527" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B1527" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1527">
-        <v>101.92</v>
+        <v>120.55</v>
       </c>
       <c r="D1527">
-        <v>0.1</v>
+        <v>4.6399999999999997</v>
       </c>
     </row>
     <row r="1528" spans="1:4" x14ac:dyDescent="0.25">
@@ -22385,13 +22376,13 @@
         <v>175</v>
       </c>
       <c r="B1528" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C1528">
-        <v>105.39</v>
+        <v>6.17</v>
       </c>
       <c r="D1528">
-        <v>3.47</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="1529" spans="1:4" x14ac:dyDescent="0.25">
@@ -22399,13 +22390,13 @@
         <v>175</v>
       </c>
       <c r="B1529" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C1529">
-        <v>105.39</v>
+        <v>23</v>
       </c>
       <c r="D1529">
-        <v>0</v>
+        <v>16.829999999999998</v>
       </c>
     </row>
     <row r="1530" spans="1:4" x14ac:dyDescent="0.25">
@@ -22413,13 +22404,13 @@
         <v>175</v>
       </c>
       <c r="B1530" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1530">
-        <v>112.72</v>
+        <v>26.61</v>
       </c>
       <c r="D1530">
-        <v>7.33</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="1531" spans="1:4" x14ac:dyDescent="0.25">
@@ -22427,97 +22418,97 @@
         <v>175</v>
       </c>
       <c r="B1531" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1531">
-        <v>141.77000000000001</v>
+        <v>83.07</v>
       </c>
       <c r="D1531">
-        <v>29.05</v>
+        <v>56.46</v>
       </c>
     </row>
     <row r="1532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1532" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B1532" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C1532">
-        <v>2.4</v>
+        <v>100.89</v>
       </c>
       <c r="D1532">
-        <v>2.4</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="1533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1533" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B1533" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C1533">
-        <v>32.5</v>
+        <v>101.51</v>
       </c>
       <c r="D1533">
-        <v>30.1</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="1534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1534" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B1534" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C1534">
-        <v>86.2</v>
+        <v>104.99</v>
       </c>
       <c r="D1534">
-        <v>53.7</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="1535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1535" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B1535" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1535">
-        <v>86.9</v>
+        <v>104.99</v>
       </c>
       <c r="D1535">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1536" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B1536" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1536">
-        <v>115.46</v>
+        <v>131.24</v>
       </c>
       <c r="D1536">
-        <v>28.56</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="1537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1537" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B1537" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1537">
-        <v>115.46</v>
+        <v>140.87</v>
       </c>
       <c r="D1537">
-        <v>0</v>
+        <v>9.6300000000000008</v>
       </c>
     </row>
     <row r="1538" spans="1:4" x14ac:dyDescent="0.25">
@@ -22525,13 +22516,13 @@
         <v>176</v>
       </c>
       <c r="B1538" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C1538">
-        <v>118.87</v>
+        <v>0.3</v>
       </c>
       <c r="D1538">
-        <v>3.41</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="1539" spans="1:4" x14ac:dyDescent="0.25">
@@ -22539,13 +22530,13 @@
         <v>176</v>
       </c>
       <c r="B1539" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C1539">
-        <v>158.76</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="D1539">
-        <v>39.89</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="1540" spans="1:4" x14ac:dyDescent="0.25">
@@ -22553,13 +22544,13 @@
         <v>176</v>
       </c>
       <c r="B1540" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1540">
-        <v>159.63999999999999</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="D1540">
-        <v>0.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1541" spans="1:4" x14ac:dyDescent="0.25">
@@ -22567,66 +22558,66 @@
         <v>176</v>
       </c>
       <c r="B1541" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1541">
-        <v>159.63999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="D1541">
-        <v>0</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="1542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1542" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B1542" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C1542">
-        <v>76.099999999999994</v>
+        <v>116.22</v>
       </c>
       <c r="D1542">
-        <v>76.099999999999994</v>
+        <v>26.72</v>
       </c>
     </row>
     <row r="1543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1543" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B1543" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C1543">
-        <v>76.099999999999994</v>
+        <v>116.32</v>
       </c>
       <c r="D1543">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="1544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1544" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B1544" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C1544">
-        <v>76.099999999999994</v>
+        <v>119.23</v>
       </c>
       <c r="D1544">
-        <v>0</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="1545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1545" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B1545" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1545">
-        <v>76.099999999999994</v>
+        <v>119.23</v>
       </c>
       <c r="D1545">
         <v>0</v>
@@ -22634,58 +22625,58 @@
     </row>
     <row r="1546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1546" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B1546" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1546">
-        <v>78.400000000000006</v>
+        <v>119.54</v>
       </c>
       <c r="D1546">
-        <v>2.2999999999999998</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="1547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1547" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B1547" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1547">
-        <v>78.400000000000006</v>
+        <v>161.59</v>
       </c>
       <c r="D1547">
-        <v>0</v>
+        <v>42.05</v>
       </c>
     </row>
     <row r="1548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1548" t="s">
         <v>177</v>
       </c>
-      <c r="B1548" t="s">
-        <v>11</v>
+      <c r="B1548" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1548">
-        <v>81.400000000000006</v>
+        <v>5.83</v>
       </c>
       <c r="D1548">
-        <v>3</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="1549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1549" t="s">
         <v>177</v>
       </c>
-      <c r="B1549" t="s">
-        <v>12</v>
+      <c r="B1549" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1549">
-        <v>97.68</v>
+        <v>53.42</v>
       </c>
       <c r="D1549">
-        <v>16.28</v>
+        <v>47.59</v>
       </c>
     </row>
     <row r="1550" spans="1:4" x14ac:dyDescent="0.25">
@@ -22693,13 +22684,13 @@
         <v>177</v>
       </c>
       <c r="B1550" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1550">
-        <v>115.91</v>
+        <v>53.42</v>
       </c>
       <c r="D1550">
-        <v>18.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1551" spans="1:4" x14ac:dyDescent="0.25">
@@ -22707,125 +22698,125 @@
         <v>177</v>
       </c>
       <c r="B1551" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1551">
-        <v>120.55</v>
+        <v>53.42</v>
       </c>
       <c r="D1551">
-        <v>4.6399999999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1552" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B1552" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C1552">
-        <v>6.17</v>
+        <v>90.49</v>
       </c>
       <c r="D1552">
-        <v>6.17</v>
+        <v>37.07</v>
       </c>
     </row>
     <row r="1553" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1553" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B1553" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C1553">
-        <v>23</v>
+        <v>90.49</v>
       </c>
       <c r="D1553">
-        <v>16.829999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1554" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1554" t="s">
-        <v>178</v>
-      </c>
-      <c r="B1554" t="s">
-        <v>7</v>
+        <v>177</v>
+      </c>
+      <c r="B1554" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1554">
-        <v>26.61</v>
+        <v>93.84</v>
       </c>
       <c r="D1554">
-        <v>3.61</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="1555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1555" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B1555" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1555">
-        <v>83.07</v>
+        <v>105.1</v>
       </c>
       <c r="D1555">
-        <v>56.46</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="1556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1556" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B1556" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1556">
-        <v>100.89</v>
+        <v>105.1</v>
       </c>
       <c r="D1556">
-        <v>17.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1557" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B1557" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1557">
-        <v>101.51</v>
+        <v>105.1</v>
       </c>
       <c r="D1557">
-        <v>0.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1558" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1558" t="s">
         <v>178</v>
       </c>
-      <c r="B1558" t="s">
-        <v>11</v>
+      <c r="B1558" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1558">
-        <v>104.99</v>
+        <v>13.27</v>
       </c>
       <c r="D1558">
-        <v>3.48</v>
+        <v>13.27</v>
       </c>
     </row>
     <row r="1559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1559" t="s">
         <v>178</v>
       </c>
-      <c r="B1559" t="s">
-        <v>12</v>
+      <c r="B1559" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1559">
-        <v>104.99</v>
+        <v>56.39</v>
       </c>
       <c r="D1559">
-        <v>0</v>
+        <v>43.12</v>
       </c>
     </row>
     <row r="1560" spans="1:4" x14ac:dyDescent="0.25">
@@ -22833,13 +22824,13 @@
         <v>178</v>
       </c>
       <c r="B1560" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1560">
-        <v>131.24</v>
+        <v>62.99</v>
       </c>
       <c r="D1560">
-        <v>26.25</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="1561" spans="1:4" x14ac:dyDescent="0.25">
@@ -22847,125 +22838,125 @@
         <v>178</v>
       </c>
       <c r="B1561" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1561">
-        <v>140.87</v>
+        <v>69.23</v>
       </c>
       <c r="D1561">
-        <v>9.6300000000000008</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="1562" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1562" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B1562" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C1562">
-        <v>0.3</v>
+        <v>79.33</v>
       </c>
       <c r="D1562">
-        <v>0.3</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="1563" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1563" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B1563" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C1563">
-        <v>10.199999999999999</v>
+        <v>79.33</v>
       </c>
       <c r="D1563">
-        <v>9.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1564" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1564" t="s">
-        <v>179</v>
-      </c>
-      <c r="B1564" t="s">
-        <v>7</v>
+        <v>178</v>
+      </c>
+      <c r="B1564" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1564">
-        <v>10.199999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="D1564">
-        <v>0</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="1565" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1565" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B1565" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1565">
-        <v>89.5</v>
+        <v>83.8</v>
       </c>
       <c r="D1565">
-        <v>79.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1566" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1566" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B1566" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1566">
-        <v>116.22</v>
+        <v>94.25</v>
       </c>
       <c r="D1566">
-        <v>26.72</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="1567" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1567" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B1567" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1567">
-        <v>116.32</v>
+        <v>94.25</v>
       </c>
       <c r="D1567">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1568" t="s">
         <v>179</v>
       </c>
-      <c r="B1568" t="s">
-        <v>11</v>
+      <c r="B1568" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1568">
-        <v>119.23</v>
+        <v>13.69</v>
       </c>
       <c r="D1568">
-        <v>2.91</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="1569" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1569" t="s">
         <v>179</v>
       </c>
-      <c r="B1569" t="s">
-        <v>12</v>
+      <c r="B1569" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1569">
-        <v>119.23</v>
+        <v>53.01</v>
       </c>
       <c r="D1569">
-        <v>0</v>
+        <v>39.32</v>
       </c>
     </row>
     <row r="1570" spans="1:4" x14ac:dyDescent="0.25">
@@ -22973,13 +22964,13 @@
         <v>179</v>
       </c>
       <c r="B1570" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1570">
-        <v>119.54</v>
+        <v>58.63</v>
       </c>
       <c r="D1570">
-        <v>0.31</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="1571" spans="1:4" x14ac:dyDescent="0.25">
@@ -22987,66 +22978,66 @@
         <v>179</v>
       </c>
       <c r="B1571" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1571">
-        <v>161.59</v>
+        <v>60.8</v>
       </c>
       <c r="D1571">
-        <v>42.05</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="1572" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1572" t="s">
-        <v>180</v>
-      </c>
-      <c r="B1572" s="2" t="s">
-        <v>5</v>
+        <v>179</v>
+      </c>
+      <c r="B1572" t="s">
+        <v>9</v>
       </c>
       <c r="C1572">
-        <v>5.83</v>
+        <v>91.33</v>
       </c>
       <c r="D1572">
-        <v>5.83</v>
+        <v>30.53</v>
       </c>
     </row>
     <row r="1573" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1573" t="s">
-        <v>180</v>
-      </c>
-      <c r="B1573" s="3" t="s">
-        <v>6</v>
+        <v>179</v>
+      </c>
+      <c r="B1573" t="s">
+        <v>10</v>
       </c>
       <c r="C1573">
-        <v>53.42</v>
+        <v>91.33</v>
       </c>
       <c r="D1573">
-        <v>47.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1574" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1574" t="s">
-        <v>180</v>
-      </c>
-      <c r="B1574" t="s">
-        <v>7</v>
+        <v>179</v>
+      </c>
+      <c r="B1574" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1574">
-        <v>53.42</v>
+        <v>94.73</v>
       </c>
       <c r="D1574">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="1575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1575" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B1575" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1575">
-        <v>53.42</v>
+        <v>94.73</v>
       </c>
       <c r="D1575">
         <v>0</v>
@@ -23054,58 +23045,58 @@
     </row>
     <row r="1576" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1576" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B1576" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1576">
-        <v>90.49</v>
+        <v>95.53</v>
       </c>
       <c r="D1576">
-        <v>37.07</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="1577" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1577" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B1577" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1577">
-        <v>90.49</v>
+        <v>105.07</v>
       </c>
       <c r="D1577">
-        <v>0</v>
+        <v>9.5399999999999991</v>
       </c>
     </row>
     <row r="1578" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1578" t="s">
         <v>180</v>
       </c>
-      <c r="B1578" s="5" t="s">
-        <v>11</v>
+      <c r="B1578" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1578">
-        <v>93.84</v>
+        <v>13.51</v>
       </c>
       <c r="D1578">
-        <v>3.35</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="1579" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1579" t="s">
         <v>180</v>
       </c>
-      <c r="B1579" t="s">
-        <v>12</v>
+      <c r="B1579" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1579">
-        <v>105.1</v>
+        <v>40.96</v>
       </c>
       <c r="D1579">
-        <v>11.26</v>
+        <v>27.45</v>
       </c>
     </row>
     <row r="1580" spans="1:4" x14ac:dyDescent="0.25">
@@ -23113,10 +23104,10 @@
         <v>180</v>
       </c>
       <c r="B1580" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1580">
-        <v>105.1</v>
+        <v>40.96</v>
       </c>
       <c r="D1580">
         <v>0</v>
@@ -23127,10 +23118,10 @@
         <v>180</v>
       </c>
       <c r="B1581" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1581">
-        <v>105.1</v>
+        <v>40.96</v>
       </c>
       <c r="D1581">
         <v>0</v>
@@ -23138,114 +23129,114 @@
     </row>
     <row r="1582" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1582" t="s">
-        <v>181</v>
-      </c>
-      <c r="B1582" s="2" t="s">
-        <v>5</v>
+        <v>180</v>
+      </c>
+      <c r="B1582" t="s">
+        <v>9</v>
       </c>
       <c r="C1582">
-        <v>13.27</v>
+        <v>50.61</v>
       </c>
       <c r="D1582">
-        <v>13.27</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="1583" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1583" t="s">
-        <v>181</v>
-      </c>
-      <c r="B1583" s="3" t="s">
-        <v>6</v>
+        <v>180</v>
+      </c>
+      <c r="B1583" t="s">
+        <v>10</v>
       </c>
       <c r="C1583">
-        <v>56.39</v>
+        <v>50.61</v>
       </c>
       <c r="D1583">
-        <v>43.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1584" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1584" t="s">
-        <v>181</v>
-      </c>
-      <c r="B1584" t="s">
-        <v>7</v>
+        <v>180</v>
+      </c>
+      <c r="B1584" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1584">
-        <v>62.99</v>
+        <v>53.61</v>
       </c>
       <c r="D1584">
-        <v>6.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1585" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1585" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B1585" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1585">
-        <v>69.23</v>
+        <v>53.61</v>
       </c>
       <c r="D1585">
-        <v>6.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1586" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1586" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B1586" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1586">
-        <v>79.33</v>
+        <v>60</v>
       </c>
       <c r="D1586">
-        <v>10.1</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="1587" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1587" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B1587" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1587">
-        <v>79.33</v>
+        <v>88.39</v>
       </c>
       <c r="D1587">
-        <v>0</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1588" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1588" t="s">
         <v>181</v>
       </c>
-      <c r="B1588" s="5" t="s">
-        <v>11</v>
+      <c r="B1588" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1588">
-        <v>82.8</v>
+        <v>25.25</v>
       </c>
       <c r="D1588">
-        <v>3.47</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="1589" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1589" t="s">
         <v>181</v>
       </c>
-      <c r="B1589" t="s">
-        <v>12</v>
+      <c r="B1589" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1589">
-        <v>83.8</v>
+        <v>64.19</v>
       </c>
       <c r="D1589">
-        <v>1</v>
+        <v>38.94</v>
       </c>
     </row>
     <row r="1590" spans="1:4" x14ac:dyDescent="0.25">
@@ -23253,13 +23244,13 @@
         <v>181</v>
       </c>
       <c r="B1590" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1590">
-        <v>94.25</v>
+        <v>64.19</v>
       </c>
       <c r="D1590">
-        <v>10.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1591" spans="1:4" x14ac:dyDescent="0.25">
@@ -23267,10 +23258,10 @@
         <v>181</v>
       </c>
       <c r="B1591" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1591">
-        <v>94.25</v>
+        <v>64.19</v>
       </c>
       <c r="D1591">
         <v>0</v>
@@ -23278,114 +23269,114 @@
     </row>
     <row r="1592" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1592" t="s">
-        <v>182</v>
-      </c>
-      <c r="B1592" s="2" t="s">
-        <v>5</v>
+        <v>181</v>
+      </c>
+      <c r="B1592" t="s">
+        <v>9</v>
       </c>
       <c r="C1592">
-        <v>13.69</v>
+        <v>78.17</v>
       </c>
       <c r="D1592">
-        <v>13.69</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="1593" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1593" t="s">
-        <v>182</v>
-      </c>
-      <c r="B1593" s="3" t="s">
-        <v>6</v>
+        <v>181</v>
+      </c>
+      <c r="B1593" t="s">
+        <v>10</v>
       </c>
       <c r="C1593">
-        <v>53.01</v>
+        <v>78.569999999999993</v>
       </c>
       <c r="D1593">
-        <v>39.32</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="1594" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1594" t="s">
-        <v>182</v>
-      </c>
-      <c r="B1594" t="s">
-        <v>7</v>
+        <v>181</v>
+      </c>
+      <c r="B1594" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1594">
-        <v>58.63</v>
+        <v>81.900000000000006</v>
       </c>
       <c r="D1594">
-        <v>5.62</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="1595" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1595" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B1595" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1595">
-        <v>60.8</v>
+        <v>84.6</v>
       </c>
       <c r="D1595">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="1596" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1596" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B1596" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1596">
-        <v>91.33</v>
+        <v>89.5</v>
       </c>
       <c r="D1596">
-        <v>30.53</v>
+        <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="1597" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1597" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B1597" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1597">
-        <v>91.33</v>
+        <v>116.9</v>
       </c>
       <c r="D1597">
-        <v>0</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="1598" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1598" t="s">
         <v>182</v>
       </c>
-      <c r="B1598" s="5" t="s">
-        <v>11</v>
+      <c r="B1598" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1598">
-        <v>94.73</v>
+        <v>3.96</v>
       </c>
       <c r="D1598">
-        <v>3.4</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="1599" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1599" t="s">
         <v>182</v>
       </c>
-      <c r="B1599" t="s">
-        <v>12</v>
+      <c r="B1599" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1599">
-        <v>94.73</v>
+        <v>34.909999999999997</v>
       </c>
       <c r="D1599">
-        <v>0</v>
+        <v>30.95</v>
       </c>
     </row>
     <row r="1600" spans="1:4" x14ac:dyDescent="0.25">
@@ -23393,13 +23384,13 @@
         <v>182</v>
       </c>
       <c r="B1600" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1600">
-        <v>95.53</v>
+        <v>53.39</v>
       </c>
       <c r="D1600">
-        <v>0.8</v>
+        <v>18.48</v>
       </c>
     </row>
     <row r="1601" spans="1:4" x14ac:dyDescent="0.25">
@@ -23407,125 +23398,125 @@
         <v>182</v>
       </c>
       <c r="B1601" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1601">
-        <v>105.07</v>
+        <v>62.65</v>
       </c>
       <c r="D1601">
-        <v>9.5399999999999991</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="1602" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1602" t="s">
-        <v>183</v>
-      </c>
-      <c r="B1602" s="2" t="s">
-        <v>5</v>
+        <v>182</v>
+      </c>
+      <c r="B1602" t="s">
+        <v>9</v>
       </c>
       <c r="C1602">
-        <v>13.51</v>
+        <v>78.319999999999993</v>
       </c>
       <c r="D1602">
-        <v>13.51</v>
+        <v>15.67</v>
       </c>
     </row>
     <row r="1603" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1603" t="s">
-        <v>183</v>
-      </c>
-      <c r="B1603" s="3" t="s">
-        <v>6</v>
+        <v>182</v>
+      </c>
+      <c r="B1603" t="s">
+        <v>10</v>
       </c>
       <c r="C1603">
-        <v>40.96</v>
+        <v>78.56</v>
       </c>
       <c r="D1603">
-        <v>27.45</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="1604" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1604" t="s">
-        <v>183</v>
-      </c>
-      <c r="B1604" t="s">
-        <v>7</v>
+        <v>182</v>
+      </c>
+      <c r="B1604" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1604">
-        <v>40.96</v>
+        <v>81.73</v>
       </c>
       <c r="D1604">
-        <v>0</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="1605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1605" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B1605" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1605">
-        <v>40.96</v>
+        <v>84.6</v>
       </c>
       <c r="D1605">
-        <v>0</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="1606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1606" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B1606" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1606">
-        <v>50.61</v>
+        <v>85.8</v>
       </c>
       <c r="D1606">
-        <v>9.65</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="1607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1607" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B1607" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1607">
-        <v>50.61</v>
+        <v>122.76</v>
       </c>
       <c r="D1607">
-        <v>0</v>
+        <v>36.96</v>
       </c>
     </row>
     <row r="1608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1608" t="s">
         <v>183</v>
       </c>
-      <c r="B1608" s="5" t="s">
-        <v>11</v>
+      <c r="B1608" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1608">
-        <v>53.61</v>
+        <v>7.88</v>
       </c>
       <c r="D1608">
-        <v>3</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="1609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1609" t="s">
         <v>183</v>
       </c>
-      <c r="B1609" t="s">
-        <v>12</v>
+      <c r="B1609" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1609">
-        <v>53.61</v>
+        <v>67.12</v>
       </c>
       <c r="D1609">
-        <v>0</v>
+        <v>59.24</v>
       </c>
     </row>
     <row r="1610" spans="1:4" x14ac:dyDescent="0.25">
@@ -23533,13 +23524,13 @@
         <v>183</v>
       </c>
       <c r="B1610" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1610">
-        <v>60</v>
+        <v>67.12</v>
       </c>
       <c r="D1610">
-        <v>6.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1611" spans="1:4" x14ac:dyDescent="0.25">
@@ -23547,66 +23538,66 @@
         <v>183</v>
       </c>
       <c r="B1611" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1611">
-        <v>88.39</v>
+        <v>67.12</v>
       </c>
       <c r="D1611">
-        <v>28.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1612" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1612" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1612" s="2" t="s">
-        <v>5</v>
+        <v>183</v>
+      </c>
+      <c r="B1612" t="s">
+        <v>9</v>
       </c>
       <c r="C1612">
-        <v>25.25</v>
+        <v>102.72</v>
       </c>
       <c r="D1612">
-        <v>25.25</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="1613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1613" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1613" s="3" t="s">
-        <v>6</v>
+        <v>183</v>
+      </c>
+      <c r="B1613" t="s">
+        <v>10</v>
       </c>
       <c r="C1613">
-        <v>64.19</v>
+        <v>102.92</v>
       </c>
       <c r="D1613">
-        <v>38.94</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="1614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1614" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1614" t="s">
-        <v>7</v>
+        <v>183</v>
+      </c>
+      <c r="B1614" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1614">
-        <v>64.19</v>
+        <v>106.22</v>
       </c>
       <c r="D1614">
-        <v>0</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="1615" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1615" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B1615" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1615">
-        <v>64.19</v>
+        <v>106.22</v>
       </c>
       <c r="D1615">
         <v>0</v>
@@ -23614,58 +23605,58 @@
     </row>
     <row r="1616" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1616" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B1616" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1616">
-        <v>78.17</v>
+        <v>106.72</v>
       </c>
       <c r="D1616">
-        <v>13.98</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1617" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1617" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B1617" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1617">
-        <v>78.569999999999993</v>
+        <v>146.52000000000001</v>
       </c>
       <c r="D1617">
-        <v>0.4</v>
+        <v>39.799999999999997</v>
       </c>
     </row>
     <row r="1618" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1618" t="s">
         <v>184</v>
       </c>
-      <c r="B1618" s="5" t="s">
-        <v>11</v>
+      <c r="B1618" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1618">
-        <v>81.900000000000006</v>
+        <v>3.26</v>
       </c>
       <c r="D1618">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="1619" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1619" t="s">
         <v>184</v>
       </c>
-      <c r="B1619" t="s">
-        <v>12</v>
+      <c r="B1619" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1619">
-        <v>84.6</v>
+        <v>94.44</v>
       </c>
       <c r="D1619">
-        <v>2.7</v>
+        <v>91.18</v>
       </c>
     </row>
     <row r="1620" spans="1:4" x14ac:dyDescent="0.25">
@@ -23673,13 +23664,13 @@
         <v>184</v>
       </c>
       <c r="B1620" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1620">
-        <v>89.5</v>
+        <v>94.44</v>
       </c>
       <c r="D1620">
-        <v>4.9000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1621" spans="1:4" x14ac:dyDescent="0.25">
@@ -23687,125 +23678,125 @@
         <v>184</v>
       </c>
       <c r="B1621" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1621">
-        <v>116.9</v>
+        <v>94.44</v>
       </c>
       <c r="D1621">
-        <v>27.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1622" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1622" t="s">
-        <v>185</v>
-      </c>
-      <c r="B1622" s="2" t="s">
-        <v>5</v>
+        <v>184</v>
+      </c>
+      <c r="B1622" t="s">
+        <v>9</v>
       </c>
       <c r="C1622">
-        <v>3.96</v>
+        <v>130.80000000000001</v>
       </c>
       <c r="D1622">
-        <v>3.96</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="1623" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1623" t="s">
-        <v>185</v>
-      </c>
-      <c r="B1623" s="3" t="s">
-        <v>6</v>
+        <v>184</v>
+      </c>
+      <c r="B1623" t="s">
+        <v>10</v>
       </c>
       <c r="C1623">
-        <v>34.909999999999997</v>
+        <v>130.80000000000001</v>
       </c>
       <c r="D1623">
-        <v>30.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1624" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1624" t="s">
-        <v>185</v>
-      </c>
-      <c r="B1624" t="s">
-        <v>7</v>
+        <v>184</v>
+      </c>
+      <c r="B1624" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1624">
-        <v>53.39</v>
+        <v>134.1</v>
       </c>
       <c r="D1624">
-        <v>18.48</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="1625" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1625" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B1625" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1625">
-        <v>62.65</v>
+        <v>174.1</v>
       </c>
       <c r="D1625">
-        <v>9.26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1626" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1626" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B1626" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1626">
-        <v>78.319999999999993</v>
+        <v>174.1</v>
       </c>
       <c r="D1626">
-        <v>15.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1627" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1627" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B1627" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1627">
-        <v>78.56</v>
+        <v>174.1</v>
       </c>
       <c r="D1627">
-        <v>0.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1628" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1628" t="s">
         <v>185</v>
       </c>
-      <c r="B1628" s="5" t="s">
-        <v>11</v>
+      <c r="B1628" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1628">
-        <v>81.73</v>
+        <v>0</v>
       </c>
       <c r="D1628">
-        <v>3.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1629" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1629" t="s">
         <v>185</v>
       </c>
-      <c r="B1629" t="s">
-        <v>12</v>
+      <c r="B1629" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1629">
-        <v>84.6</v>
+        <v>107.01</v>
       </c>
       <c r="D1629">
-        <v>2.87</v>
+        <v>107.01</v>
       </c>
     </row>
     <row r="1630" spans="1:4" x14ac:dyDescent="0.25">
@@ -23813,13 +23804,13 @@
         <v>185</v>
       </c>
       <c r="B1630" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1630">
-        <v>85.8</v>
+        <v>109.41</v>
       </c>
       <c r="D1630">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="1631" spans="1:4" x14ac:dyDescent="0.25">
@@ -23827,66 +23818,66 @@
         <v>185</v>
       </c>
       <c r="B1631" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1631">
-        <v>122.76</v>
+        <v>127</v>
       </c>
       <c r="D1631">
-        <v>36.96</v>
+        <v>17.59</v>
       </c>
     </row>
     <row r="1632" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1632" t="s">
-        <v>186</v>
-      </c>
-      <c r="B1632" s="2" t="s">
-        <v>5</v>
+        <v>185</v>
+      </c>
+      <c r="B1632" t="s">
+        <v>9</v>
       </c>
       <c r="C1632">
-        <v>7.88</v>
+        <v>129.5</v>
       </c>
       <c r="D1632">
-        <v>7.88</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="1633" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1633" t="s">
-        <v>186</v>
-      </c>
-      <c r="B1633" s="3" t="s">
-        <v>6</v>
+        <v>185</v>
+      </c>
+      <c r="B1633" t="s">
+        <v>10</v>
       </c>
       <c r="C1633">
-        <v>67.12</v>
+        <v>131.69999999999999</v>
       </c>
       <c r="D1633">
-        <v>59.24</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="1634" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1634" t="s">
-        <v>186</v>
-      </c>
-      <c r="B1634" t="s">
-        <v>7</v>
+        <v>185</v>
+      </c>
+      <c r="B1634" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1634">
-        <v>67.12</v>
+        <v>134.80000000000001</v>
       </c>
       <c r="D1634">
-        <v>0</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="1635" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1635" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B1635" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1635">
-        <v>67.12</v>
+        <v>134.80000000000001</v>
       </c>
       <c r="D1635">
         <v>0</v>
@@ -23894,58 +23885,58 @@
     </row>
     <row r="1636" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1636" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B1636" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1636">
-        <v>102.72</v>
+        <v>139.5</v>
       </c>
       <c r="D1636">
-        <v>35.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="1637" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1637" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B1637" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1637">
-        <v>102.92</v>
+        <v>174.25</v>
       </c>
       <c r="D1637">
-        <v>0.2</v>
+        <v>34.75</v>
       </c>
     </row>
     <row r="1638" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1638" t="s">
         <v>186</v>
       </c>
-      <c r="B1638" s="5" t="s">
-        <v>11</v>
+      <c r="B1638" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1638">
-        <v>106.22</v>
+        <v>26</v>
       </c>
       <c r="D1638">
-        <v>3.3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1639" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1639" t="s">
         <v>186</v>
       </c>
-      <c r="B1639" t="s">
-        <v>12</v>
+      <c r="B1639" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1639">
-        <v>106.22</v>
+        <v>58</v>
       </c>
       <c r="D1639">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1640" spans="1:4" x14ac:dyDescent="0.25">
@@ -23953,13 +23944,13 @@
         <v>186</v>
       </c>
       <c r="B1640" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1640">
-        <v>106.72</v>
+        <v>58</v>
       </c>
       <c r="D1640">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1641" spans="1:4" x14ac:dyDescent="0.25">
@@ -23967,66 +23958,66 @@
         <v>186</v>
       </c>
       <c r="B1641" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1641">
-        <v>146.52000000000001</v>
+        <v>58</v>
       </c>
       <c r="D1641">
-        <v>39.799999999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1642" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1642" t="s">
-        <v>187</v>
-      </c>
-      <c r="B1642" s="2" t="s">
-        <v>5</v>
+        <v>186</v>
+      </c>
+      <c r="B1642" t="s">
+        <v>9</v>
       </c>
       <c r="C1642">
-        <v>3.26</v>
+        <v>77.81</v>
       </c>
       <c r="D1642">
-        <v>3.26</v>
+        <v>19.809999999999999</v>
       </c>
     </row>
     <row r="1643" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1643" t="s">
-        <v>187</v>
-      </c>
-      <c r="B1643" s="3" t="s">
-        <v>6</v>
+        <v>186</v>
+      </c>
+      <c r="B1643" t="s">
+        <v>10</v>
       </c>
       <c r="C1643">
-        <v>94.44</v>
+        <v>78.36</v>
       </c>
       <c r="D1643">
-        <v>91.18</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="1644" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1644" t="s">
-        <v>187</v>
-      </c>
-      <c r="B1644" t="s">
-        <v>7</v>
+        <v>186</v>
+      </c>
+      <c r="B1644" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1644">
-        <v>94.44</v>
+        <v>81.7</v>
       </c>
       <c r="D1644">
-        <v>0</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="1645" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1645" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B1645" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1645">
-        <v>94.44</v>
+        <v>81.7</v>
       </c>
       <c r="D1645">
         <v>0</v>
@@ -24034,58 +24025,58 @@
     </row>
     <row r="1646" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1646" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B1646" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1646">
-        <v>130.80000000000001</v>
+        <v>87.99</v>
       </c>
       <c r="D1646">
-        <v>36.36</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="1647" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1647" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B1647" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1647">
-        <v>130.80000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="D1647">
-        <v>0</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="1648" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1648" t="s">
         <v>187</v>
       </c>
-      <c r="B1648" s="5" t="s">
-        <v>11</v>
+      <c r="B1648" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1648">
-        <v>134.1</v>
+        <v>7.3</v>
       </c>
       <c r="D1648">
-        <v>3.3</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="1649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1649" t="s">
         <v>187</v>
       </c>
-      <c r="B1649" t="s">
-        <v>12</v>
+      <c r="B1649" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1649">
-        <v>174.1</v>
+        <v>69.7</v>
       </c>
       <c r="D1649">
-        <v>40</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="1650" spans="1:4" x14ac:dyDescent="0.25">
@@ -24093,13 +24084,13 @@
         <v>187</v>
       </c>
       <c r="B1650" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1650">
-        <v>174.1</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="D1650">
-        <v>0</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="1651" spans="1:4" x14ac:dyDescent="0.25">
@@ -24107,125 +24098,125 @@
         <v>187</v>
       </c>
       <c r="B1651" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1651">
-        <v>174.1</v>
+        <v>111.5</v>
       </c>
       <c r="D1651">
-        <v>0</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="1652" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1652" t="s">
-        <v>188</v>
-      </c>
-      <c r="B1652" s="2" t="s">
-        <v>5</v>
+        <v>187</v>
+      </c>
+      <c r="B1652" t="s">
+        <v>9</v>
       </c>
       <c r="C1652">
-        <v>0</v>
+        <v>113.7</v>
       </c>
       <c r="D1652">
-        <v>0</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="1653" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1653" t="s">
-        <v>188</v>
-      </c>
-      <c r="B1653" s="3" t="s">
-        <v>6</v>
+        <v>187</v>
+      </c>
+      <c r="B1653" t="s">
+        <v>10</v>
       </c>
       <c r="C1653">
-        <v>107.01</v>
+        <v>113.7</v>
       </c>
       <c r="D1653">
-        <v>107.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1654" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1654" t="s">
-        <v>188</v>
-      </c>
-      <c r="B1654" t="s">
-        <v>7</v>
+        <v>187</v>
+      </c>
+      <c r="B1654" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1654">
-        <v>109.41</v>
+        <v>117.05</v>
       </c>
       <c r="D1654">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="1655" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1655" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B1655" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1655">
-        <v>127</v>
+        <v>117.05</v>
       </c>
       <c r="D1655">
-        <v>17.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1656" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1656" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B1656" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1656">
-        <v>129.5</v>
+        <v>120.48</v>
       </c>
       <c r="D1656">
-        <v>2.5</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="1657" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1657" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B1657" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1657">
-        <v>131.69999999999999</v>
+        <v>151.03</v>
       </c>
       <c r="D1657">
-        <v>2.2000000000000002</v>
+        <v>30.55</v>
       </c>
     </row>
     <row r="1658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1658" t="s">
         <v>188</v>
       </c>
-      <c r="B1658" s="5" t="s">
-        <v>11</v>
+      <c r="B1658" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1658">
-        <v>134.80000000000001</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="D1658">
-        <v>3.1</v>
+        <v>4.6900000000000004</v>
       </c>
     </row>
     <row r="1659" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1659" t="s">
         <v>188</v>
       </c>
-      <c r="B1659" t="s">
-        <v>12</v>
+      <c r="B1659" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1659">
-        <v>134.80000000000001</v>
+        <v>42</v>
       </c>
       <c r="D1659">
-        <v>0</v>
+        <v>37.31</v>
       </c>
     </row>
     <row r="1660" spans="1:4" x14ac:dyDescent="0.25">
@@ -24233,13 +24224,13 @@
         <v>188</v>
       </c>
       <c r="B1660" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1660">
-        <v>139.5</v>
+        <v>42</v>
       </c>
       <c r="D1660">
-        <v>4.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1661" spans="1:4" x14ac:dyDescent="0.25">
@@ -24247,125 +24238,125 @@
         <v>188</v>
       </c>
       <c r="B1661" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1661">
-        <v>174.25</v>
+        <v>42</v>
       </c>
       <c r="D1661">
-        <v>34.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1662" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1662" t="s">
-        <v>189</v>
-      </c>
-      <c r="B1662" s="2" t="s">
-        <v>5</v>
+        <v>188</v>
+      </c>
+      <c r="B1662" t="s">
+        <v>9</v>
       </c>
       <c r="C1662">
-        <v>26</v>
+        <v>93.86</v>
       </c>
       <c r="D1662">
-        <v>26</v>
+        <v>51.86</v>
       </c>
     </row>
     <row r="1663" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1663" t="s">
-        <v>189</v>
-      </c>
-      <c r="B1663" s="3" t="s">
-        <v>6</v>
+        <v>188</v>
+      </c>
+      <c r="B1663" t="s">
+        <v>10</v>
       </c>
       <c r="C1663">
-        <v>58</v>
+        <v>93.86</v>
       </c>
       <c r="D1663">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1664" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1664" t="s">
-        <v>189</v>
-      </c>
-      <c r="B1664" t="s">
-        <v>7</v>
+        <v>188</v>
+      </c>
+      <c r="B1664" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1664">
-        <v>58</v>
+        <v>97.15</v>
       </c>
       <c r="D1664">
-        <v>0</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="1665" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1665" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B1665" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1665">
-        <v>58</v>
+        <v>98.95</v>
       </c>
       <c r="D1665">
-        <v>0</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="1666" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1666" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B1666" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1666">
-        <v>77.81</v>
+        <v>99.15</v>
       </c>
       <c r="D1666">
-        <v>19.809999999999999</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="1667" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1667" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B1667" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1667">
-        <v>78.36</v>
+        <v>133.65</v>
       </c>
       <c r="D1667">
-        <v>0.55000000000000004</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="1668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1668" t="s">
         <v>189</v>
       </c>
-      <c r="B1668" s="5" t="s">
-        <v>11</v>
+      <c r="B1668" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1668">
-        <v>81.7</v>
+        <v>1.5</v>
       </c>
       <c r="D1668">
-        <v>3.34</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1669" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1669" t="s">
         <v>189</v>
       </c>
-      <c r="B1669" t="s">
-        <v>12</v>
+      <c r="B1669" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1669">
-        <v>81.7</v>
+        <v>26.59</v>
       </c>
       <c r="D1669">
-        <v>0</v>
+        <v>25.09</v>
       </c>
     </row>
     <row r="1670" spans="1:4" x14ac:dyDescent="0.25">
@@ -24373,13 +24364,13 @@
         <v>189</v>
       </c>
       <c r="B1670" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1670">
-        <v>87.99</v>
+        <v>26.59</v>
       </c>
       <c r="D1670">
-        <v>6.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1671" spans="1:4" x14ac:dyDescent="0.25">
@@ -24387,125 +24378,125 @@
         <v>189</v>
       </c>
       <c r="B1671" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1671">
-        <v>94.5</v>
+        <v>26.59</v>
       </c>
       <c r="D1671">
-        <v>6.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1672" t="s">
-        <v>190</v>
-      </c>
-      <c r="B1672" s="2" t="s">
-        <v>5</v>
+        <v>189</v>
+      </c>
+      <c r="B1672" t="s">
+        <v>9</v>
       </c>
       <c r="C1672">
-        <v>7.3</v>
+        <v>76.34</v>
       </c>
       <c r="D1672">
-        <v>7.3</v>
+        <v>49.75</v>
       </c>
     </row>
     <row r="1673" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1673" t="s">
-        <v>190</v>
-      </c>
-      <c r="B1673" s="3" t="s">
-        <v>6</v>
+        <v>189</v>
+      </c>
+      <c r="B1673" t="s">
+        <v>10</v>
       </c>
       <c r="C1673">
-        <v>69.7</v>
+        <v>76.34</v>
       </c>
       <c r="D1673">
-        <v>62.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1674" t="s">
-        <v>190</v>
-      </c>
-      <c r="B1674" t="s">
-        <v>7</v>
+        <v>189</v>
+      </c>
+      <c r="B1674" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1674">
-        <v>72.900000000000006</v>
+        <v>79.8</v>
       </c>
       <c r="D1674">
-        <v>3.2</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="1675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1675" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B1675" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1675">
-        <v>111.5</v>
+        <v>79.8</v>
       </c>
       <c r="D1675">
-        <v>38.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1676" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1676" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B1676" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1676">
-        <v>113.7</v>
+        <v>80.099999999999994</v>
       </c>
       <c r="D1676">
-        <v>2.2000000000000002</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="1677" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1677" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B1677" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1677">
-        <v>113.7</v>
+        <v>116.74</v>
       </c>
       <c r="D1677">
-        <v>0</v>
+        <v>36.64</v>
       </c>
     </row>
     <row r="1678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1678" t="s">
         <v>190</v>
       </c>
-      <c r="B1678" s="5" t="s">
-        <v>11</v>
+      <c r="B1678" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1678">
-        <v>117.05</v>
+        <v>14.53</v>
       </c>
       <c r="D1678">
-        <v>3.35</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="1679" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1679" t="s">
         <v>190</v>
       </c>
-      <c r="B1679" t="s">
-        <v>12</v>
+      <c r="B1679" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1679">
-        <v>117.05</v>
+        <v>30.06</v>
       </c>
       <c r="D1679">
-        <v>0</v>
+        <v>15.53</v>
       </c>
     </row>
     <row r="1680" spans="1:4" x14ac:dyDescent="0.25">
@@ -24513,13 +24504,13 @@
         <v>190</v>
       </c>
       <c r="B1680" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1680">
-        <v>120.48</v>
+        <v>49.5</v>
       </c>
       <c r="D1680">
-        <v>3.43</v>
+        <v>19.440000000000001</v>
       </c>
     </row>
     <row r="1681" spans="1:4" x14ac:dyDescent="0.25">
@@ -24527,66 +24518,66 @@
         <v>190</v>
       </c>
       <c r="B1681" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1681">
-        <v>151.03</v>
+        <v>53.49</v>
       </c>
       <c r="D1681">
-        <v>30.55</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="1682" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1682" t="s">
-        <v>191</v>
-      </c>
-      <c r="B1682" s="2" t="s">
-        <v>5</v>
+        <v>190</v>
+      </c>
+      <c r="B1682" t="s">
+        <v>9</v>
       </c>
       <c r="C1682">
-        <v>4.6900000000000004</v>
+        <v>78.95</v>
       </c>
       <c r="D1682">
-        <v>4.6900000000000004</v>
+        <v>25.46</v>
       </c>
     </row>
     <row r="1683" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1683" t="s">
-        <v>191</v>
-      </c>
-      <c r="B1683" s="3" t="s">
-        <v>6</v>
+        <v>190</v>
+      </c>
+      <c r="B1683" t="s">
+        <v>10</v>
       </c>
       <c r="C1683">
-        <v>42</v>
+        <v>78.95</v>
       </c>
       <c r="D1683">
-        <v>37.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1684" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1684" t="s">
-        <v>191</v>
-      </c>
-      <c r="B1684" t="s">
-        <v>7</v>
+        <v>190</v>
+      </c>
+      <c r="B1684" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1684">
-        <v>42</v>
+        <v>82.32</v>
       </c>
       <c r="D1684">
-        <v>0</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="1685" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1685" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B1685" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1685">
-        <v>42</v>
+        <v>82.32</v>
       </c>
       <c r="D1685">
         <v>0</v>
@@ -24594,58 +24585,58 @@
     </row>
     <row r="1686" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1686" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B1686" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1686">
-        <v>93.86</v>
+        <v>88.89</v>
       </c>
       <c r="D1686">
-        <v>51.86</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="1687" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1687" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B1687" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1687">
-        <v>93.86</v>
+        <v>116.25</v>
       </c>
       <c r="D1687">
-        <v>0</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="1688" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1688" t="s">
         <v>191</v>
       </c>
-      <c r="B1688" s="5" t="s">
-        <v>11</v>
+      <c r="B1688" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1688">
-        <v>97.15</v>
+        <v>14.3</v>
       </c>
       <c r="D1688">
-        <v>3.29</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="1689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1689" t="s">
         <v>191</v>
       </c>
-      <c r="B1689" t="s">
-        <v>12</v>
+      <c r="B1689" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1689">
-        <v>98.95</v>
+        <v>29.05</v>
       </c>
       <c r="D1689">
-        <v>1.8</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="1690" spans="1:4" x14ac:dyDescent="0.25">
@@ -24653,13 +24644,13 @@
         <v>191</v>
       </c>
       <c r="B1690" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1690">
-        <v>99.15</v>
+        <v>66.8</v>
       </c>
       <c r="D1690">
-        <v>0.2</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="1691" spans="1:4" x14ac:dyDescent="0.25">
@@ -24667,66 +24658,66 @@
         <v>191</v>
       </c>
       <c r="B1691" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1691">
-        <v>133.65</v>
+        <v>81.99</v>
       </c>
       <c r="D1691">
-        <v>34.5</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="1692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1692" t="s">
-        <v>192</v>
-      </c>
-      <c r="B1692" s="2" t="s">
-        <v>5</v>
+        <v>191</v>
+      </c>
+      <c r="B1692" t="s">
+        <v>9</v>
       </c>
       <c r="C1692">
-        <v>1.5</v>
+        <v>94.44</v>
       </c>
       <c r="D1692">
-        <v>1.5</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="1693" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1693" t="s">
-        <v>192</v>
-      </c>
-      <c r="B1693" s="3" t="s">
-        <v>6</v>
+        <v>191</v>
+      </c>
+      <c r="B1693" t="s">
+        <v>10</v>
       </c>
       <c r="C1693">
-        <v>26.59</v>
+        <v>95.45</v>
       </c>
       <c r="D1693">
-        <v>25.09</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="1694" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1694" t="s">
-        <v>192</v>
-      </c>
-      <c r="B1694" t="s">
-        <v>7</v>
+        <v>191</v>
+      </c>
+      <c r="B1694" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1694">
-        <v>26.59</v>
+        <v>98.6</v>
       </c>
       <c r="D1694">
-        <v>0</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="1695" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1695" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B1695" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1695">
-        <v>26.59</v>
+        <v>98.6</v>
       </c>
       <c r="D1695">
         <v>0</v>
@@ -24734,58 +24725,58 @@
     </row>
     <row r="1696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1696" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B1696" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1696">
-        <v>76.34</v>
+        <v>107.44</v>
       </c>
       <c r="D1696">
-        <v>49.75</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="1697" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1697" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B1697" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1697">
-        <v>76.34</v>
+        <v>134.88999999999999</v>
       </c>
       <c r="D1697">
-        <v>0</v>
+        <v>27.45</v>
       </c>
     </row>
     <row r="1698" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1698" t="s">
         <v>192</v>
       </c>
-      <c r="B1698" s="5" t="s">
-        <v>11</v>
+      <c r="B1698" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1698">
-        <v>79.8</v>
+        <v>27.3</v>
       </c>
       <c r="D1698">
-        <v>3.46</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="1699" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1699" t="s">
         <v>192</v>
       </c>
-      <c r="B1699" t="s">
-        <v>12</v>
+      <c r="B1699" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1699">
-        <v>79.8</v>
+        <v>103.35</v>
       </c>
       <c r="D1699">
-        <v>0</v>
+        <v>76.05</v>
       </c>
     </row>
     <row r="1700" spans="1:4" x14ac:dyDescent="0.25">
@@ -24793,13 +24784,13 @@
         <v>192</v>
       </c>
       <c r="B1700" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1700">
-        <v>80.099999999999994</v>
+        <v>124.13</v>
       </c>
       <c r="D1700">
-        <v>0.3</v>
+        <v>20.78</v>
       </c>
     </row>
     <row r="1701" spans="1:4" x14ac:dyDescent="0.25">
@@ -24807,125 +24798,125 @@
         <v>192</v>
       </c>
       <c r="B1701" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1701">
-        <v>116.74</v>
+        <v>127.26</v>
       </c>
       <c r="D1701">
-        <v>36.64</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="1702" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1702" t="s">
-        <v>193</v>
-      </c>
-      <c r="B1702" s="2" t="s">
-        <v>5</v>
+        <v>192</v>
+      </c>
+      <c r="B1702" t="s">
+        <v>9</v>
       </c>
       <c r="C1702">
-        <v>14.53</v>
+        <v>147.19999999999999</v>
       </c>
       <c r="D1702">
-        <v>14.53</v>
+        <v>19.940000000000001</v>
       </c>
     </row>
     <row r="1703" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1703" t="s">
-        <v>193</v>
-      </c>
-      <c r="B1703" s="3" t="s">
-        <v>6</v>
+        <v>192</v>
+      </c>
+      <c r="B1703" t="s">
+        <v>10</v>
       </c>
       <c r="C1703">
-        <v>30.06</v>
+        <v>147.4</v>
       </c>
       <c r="D1703">
-        <v>15.53</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="1704" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1704" t="s">
-        <v>193</v>
-      </c>
-      <c r="B1704" t="s">
-        <v>7</v>
+        <v>192</v>
+      </c>
+      <c r="B1704" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1704">
-        <v>49.5</v>
+        <v>150.72999999999999</v>
       </c>
       <c r="D1704">
-        <v>19.440000000000001</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="1705" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1705" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B1705" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1705">
-        <v>53.49</v>
+        <v>150.72999999999999</v>
       </c>
       <c r="D1705">
-        <v>3.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1706" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1706" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B1706" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1706">
-        <v>78.95</v>
+        <v>170.82</v>
       </c>
       <c r="D1706">
-        <v>25.46</v>
+        <v>20.09</v>
       </c>
     </row>
     <row r="1707" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1707" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B1707" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1707">
-        <v>78.95</v>
+        <v>192.21</v>
       </c>
       <c r="D1707">
-        <v>0</v>
+        <v>21.39</v>
       </c>
     </row>
     <row r="1708" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1708" t="s">
         <v>193</v>
       </c>
-      <c r="B1708" s="5" t="s">
-        <v>11</v>
+      <c r="B1708" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1708">
-        <v>82.32</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="D1708">
-        <v>3.37</v>
+        <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="1709" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1709" t="s">
         <v>193</v>
       </c>
-      <c r="B1709" t="s">
-        <v>12</v>
+      <c r="B1709" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1709">
-        <v>82.32</v>
+        <v>84.05</v>
       </c>
       <c r="D1709">
-        <v>0</v>
+        <v>79.150000000000006</v>
       </c>
     </row>
     <row r="1710" spans="1:4" x14ac:dyDescent="0.25">
@@ -24933,13 +24924,13 @@
         <v>193</v>
       </c>
       <c r="B1710" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1710">
-        <v>88.89</v>
+        <v>84.05</v>
       </c>
       <c r="D1710">
-        <v>6.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1711" spans="1:4" x14ac:dyDescent="0.25">
@@ -24947,125 +24938,125 @@
         <v>193</v>
       </c>
       <c r="B1711" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1711">
-        <v>116.25</v>
+        <v>84.05</v>
       </c>
       <c r="D1711">
-        <v>27.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1712" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1712" t="s">
-        <v>194</v>
-      </c>
-      <c r="B1712" s="2" t="s">
-        <v>5</v>
+        <v>193</v>
+      </c>
+      <c r="B1712" t="s">
+        <v>9</v>
       </c>
       <c r="C1712">
-        <v>14.3</v>
+        <v>115</v>
       </c>
       <c r="D1712">
-        <v>14.3</v>
+        <v>30.95</v>
       </c>
     </row>
     <row r="1713" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1713" t="s">
-        <v>194</v>
-      </c>
-      <c r="B1713" s="3" t="s">
-        <v>6</v>
+        <v>193</v>
+      </c>
+      <c r="B1713" t="s">
+        <v>10</v>
       </c>
       <c r="C1713">
-        <v>29.05</v>
+        <v>115</v>
       </c>
       <c r="D1713">
-        <v>14.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1714" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1714" t="s">
-        <v>194</v>
-      </c>
-      <c r="B1714" t="s">
-        <v>7</v>
+        <v>193</v>
+      </c>
+      <c r="B1714" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1714">
-        <v>66.8</v>
+        <v>117.86</v>
       </c>
       <c r="D1714">
-        <v>37.75</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="1715" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1715" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B1715" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1715">
-        <v>81.99</v>
+        <v>158.55000000000001</v>
       </c>
       <c r="D1715">
-        <v>15.19</v>
+        <v>40.69</v>
       </c>
     </row>
     <row r="1716" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1716" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B1716" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1716">
-        <v>94.44</v>
+        <v>158.55000000000001</v>
       </c>
       <c r="D1716">
-        <v>12.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1717" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1717" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B1717" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1717">
-        <v>95.45</v>
+        <v>158.55000000000001</v>
       </c>
       <c r="D1717">
-        <v>1.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1718" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1718" t="s">
         <v>194</v>
       </c>
-      <c r="B1718" s="5" t="s">
-        <v>11</v>
+      <c r="B1718" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1718">
-        <v>98.6</v>
+        <v>5.5</v>
       </c>
       <c r="D1718">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="1719" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1719" t="s">
         <v>194</v>
       </c>
-      <c r="B1719" t="s">
-        <v>12</v>
+      <c r="B1719" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1719">
-        <v>98.6</v>
+        <v>58.56</v>
       </c>
       <c r="D1719">
-        <v>0</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="1720" spans="1:4" x14ac:dyDescent="0.25">
@@ -25073,13 +25064,13 @@
         <v>194</v>
       </c>
       <c r="B1720" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1720">
-        <v>107.44</v>
+        <v>65.27</v>
       </c>
       <c r="D1720">
-        <v>8.84</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="1721" spans="1:4" x14ac:dyDescent="0.25">
@@ -25087,125 +25078,125 @@
         <v>194</v>
       </c>
       <c r="B1721" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1721">
-        <v>134.88999999999999</v>
+        <v>79.94</v>
       </c>
       <c r="D1721">
-        <v>27.45</v>
+        <v>14.67</v>
       </c>
     </row>
     <row r="1722" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1722" t="s">
-        <v>195</v>
-      </c>
-      <c r="B1722" s="2" t="s">
-        <v>5</v>
+        <v>194</v>
+      </c>
+      <c r="B1722" t="s">
+        <v>9</v>
       </c>
       <c r="C1722">
-        <v>27.3</v>
+        <v>86.3</v>
       </c>
       <c r="D1722">
-        <v>27.3</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="1723" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1723" t="s">
-        <v>195</v>
-      </c>
-      <c r="B1723" s="3" t="s">
-        <v>6</v>
+        <v>194</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>10</v>
       </c>
       <c r="C1723">
-        <v>103.35</v>
+        <v>86.3</v>
       </c>
       <c r="D1723">
-        <v>76.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1724" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1724" t="s">
-        <v>195</v>
-      </c>
-      <c r="B1724" t="s">
-        <v>7</v>
+        <v>194</v>
+      </c>
+      <c r="B1724" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1724">
-        <v>124.13</v>
+        <v>89.15</v>
       </c>
       <c r="D1724">
-        <v>20.78</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="1725" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1725" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B1725" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1725">
-        <v>127.26</v>
+        <v>89.15</v>
       </c>
       <c r="D1725">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1726" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1726" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B1726" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1726">
-        <v>147.19999999999999</v>
+        <v>128.68</v>
       </c>
       <c r="D1726">
-        <v>19.940000000000001</v>
+        <v>39.53</v>
       </c>
     </row>
     <row r="1727" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1727" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B1727" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1727">
-        <v>147.4</v>
+        <v>130.43</v>
       </c>
       <c r="D1727">
-        <v>0.2</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="1728" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1728" t="s">
         <v>195</v>
       </c>
-      <c r="B1728" s="5" t="s">
-        <v>11</v>
+      <c r="B1728" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C1728">
-        <v>150.72999999999999</v>
+        <v>21</v>
       </c>
       <c r="D1728">
-        <v>3.33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1729" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1729" t="s">
         <v>195</v>
       </c>
-      <c r="B1729" t="s">
-        <v>12</v>
+      <c r="B1729" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1729">
-        <v>150.72999999999999</v>
+        <v>71.099999999999994</v>
       </c>
       <c r="D1729">
-        <v>0</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1730" spans="1:4" x14ac:dyDescent="0.25">
@@ -25213,13 +25204,13 @@
         <v>195</v>
       </c>
       <c r="B1730" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1730">
-        <v>170.82</v>
+        <v>73.099999999999994</v>
       </c>
       <c r="D1730">
-        <v>20.09</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1731" spans="1:4" x14ac:dyDescent="0.25">
@@ -25227,66 +25218,66 @@
         <v>195</v>
       </c>
       <c r="B1731" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C1731">
-        <v>192.21</v>
+        <v>82.1</v>
       </c>
       <c r="D1731">
-        <v>21.39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1732" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1732" t="s">
-        <v>196</v>
-      </c>
-      <c r="B1732" s="2" t="s">
-        <v>5</v>
+        <v>195</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>9</v>
       </c>
       <c r="C1732">
-        <v>4.9000000000000004</v>
+        <v>95.9</v>
       </c>
       <c r="D1732">
-        <v>4.9000000000000004</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="1733" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1733" t="s">
-        <v>196</v>
-      </c>
-      <c r="B1733" s="3" t="s">
-        <v>6</v>
+        <v>195</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>10</v>
       </c>
       <c r="C1733">
-        <v>84.05</v>
+        <v>100.2</v>
       </c>
       <c r="D1733">
-        <v>79.150000000000006</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="1734" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1734" t="s">
-        <v>196</v>
-      </c>
-      <c r="B1734" t="s">
-        <v>7</v>
+        <v>195</v>
+      </c>
+      <c r="B1734" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C1734">
-        <v>84.05</v>
+        <v>103.2</v>
       </c>
       <c r="D1734">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1735" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1735" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B1735" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C1735">
-        <v>84.05</v>
+        <v>103.2</v>
       </c>
       <c r="D1735">
         <v>0</v>
@@ -25294,365 +25285,29 @@
     </row>
     <row r="1736" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1736" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B1736" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C1736">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="D1736">
-        <v>30.95</v>
+        <v>38.799999999999997</v>
       </c>
     </row>
     <row r="1737" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1737" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B1737" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1737">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="D1737">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1738" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1738" t="s">
-        <v>196</v>
-      </c>
-      <c r="B1738" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1738">
-        <v>117.86</v>
-      </c>
-      <c r="D1738">
-        <v>2.86</v>
-      </c>
-    </row>
-    <row r="1739" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1739" t="s">
-        <v>196</v>
-      </c>
-      <c r="B1739" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1739">
-        <v>158.55000000000001</v>
-      </c>
-      <c r="D1739">
-        <v>40.69</v>
-      </c>
-    </row>
-    <row r="1740" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1740" t="s">
-        <v>196</v>
-      </c>
-      <c r="B1740" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1740">
-        <v>158.55000000000001</v>
-      </c>
-      <c r="D1740">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1741" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1741" t="s">
-        <v>196</v>
-      </c>
-      <c r="B1741" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1741">
-        <v>158.55000000000001</v>
-      </c>
-      <c r="D1741">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1742" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1742" t="s">
-        <v>197</v>
-      </c>
-      <c r="B1742" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1742">
-        <v>5.5</v>
-      </c>
-      <c r="D1742">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="1743" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1743" t="s">
-        <v>197</v>
-      </c>
-      <c r="B1743" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1743">
-        <v>58.56</v>
-      </c>
-      <c r="D1743">
-        <v>53.06</v>
-      </c>
-    </row>
-    <row r="1744" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1744" t="s">
-        <v>197</v>
-      </c>
-      <c r="B1744" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1744">
-        <v>65.27</v>
-      </c>
-      <c r="D1744">
-        <v>6.71</v>
-      </c>
-    </row>
-    <row r="1745" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1745" t="s">
-        <v>197</v>
-      </c>
-      <c r="B1745" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1745">
-        <v>79.94</v>
-      </c>
-      <c r="D1745">
-        <v>14.67</v>
-      </c>
-    </row>
-    <row r="1746" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1746" t="s">
-        <v>197</v>
-      </c>
-      <c r="B1746" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1746">
-        <v>86.3</v>
-      </c>
-      <c r="D1746">
-        <v>6.36</v>
-      </c>
-    </row>
-    <row r="1747" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1747" t="s">
-        <v>197</v>
-      </c>
-      <c r="B1747" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1747">
-        <v>86.3</v>
-      </c>
-      <c r="D1747">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1748" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1748" t="s">
-        <v>197</v>
-      </c>
-      <c r="B1748" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1748">
-        <v>89.15</v>
-      </c>
-      <c r="D1748">
-        <v>2.85</v>
-      </c>
-    </row>
-    <row r="1749" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1749" t="s">
-        <v>197</v>
-      </c>
-      <c r="B1749" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1749">
-        <v>89.15</v>
-      </c>
-      <c r="D1749">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1750" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1750" t="s">
-        <v>197</v>
-      </c>
-      <c r="B1750" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1750">
-        <v>128.68</v>
-      </c>
-      <c r="D1750">
-        <v>39.53</v>
-      </c>
-    </row>
-    <row r="1751" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1751" t="s">
-        <v>197</v>
-      </c>
-      <c r="B1751" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1751">
-        <v>130.43</v>
-      </c>
-      <c r="D1751">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="1752" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1752" t="s">
-        <v>198</v>
-      </c>
-      <c r="B1752" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1752">
-        <v>21</v>
-      </c>
-      <c r="D1752">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="1753" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1753" t="s">
-        <v>198</v>
-      </c>
-      <c r="B1753" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1753">
-        <v>71.099999999999994</v>
-      </c>
-      <c r="D1753">
-        <v>50.1</v>
-      </c>
-    </row>
-    <row r="1754" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1754" t="s">
-        <v>198</v>
-      </c>
-      <c r="B1754" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1754">
-        <v>73.099999999999994</v>
-      </c>
-      <c r="D1754">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1755" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1755" t="s">
-        <v>198</v>
-      </c>
-      <c r="B1755" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1755">
-        <v>82.1</v>
-      </c>
-      <c r="D1755">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="1756" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1756" t="s">
-        <v>198</v>
-      </c>
-      <c r="B1756" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1756">
-        <v>95.9</v>
-      </c>
-      <c r="D1756">
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="1757" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1757" t="s">
-        <v>198</v>
-      </c>
-      <c r="B1757" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1757">
-        <v>100.2</v>
-      </c>
-      <c r="D1757">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="1758" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1758" t="s">
-        <v>198</v>
-      </c>
-      <c r="B1758" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1758">
-        <v>103.2</v>
-      </c>
-      <c r="D1758">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1759" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1759" t="s">
-        <v>198</v>
-      </c>
-      <c r="B1759" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1759">
-        <v>103.2</v>
-      </c>
-      <c r="D1759">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1760" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1760" t="s">
-        <v>198</v>
-      </c>
-      <c r="B1760" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1760">
-        <v>142</v>
-      </c>
-      <c r="D1760">
-        <v>38.799999999999997</v>
-      </c>
-    </row>
-    <row r="1761" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1761" t="s">
-        <v>198</v>
-      </c>
-      <c r="B1761" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1761">
-        <v>142</v>
-      </c>
-      <c r="D1761">
         <v>0</v>
       </c>
     </row>
